--- a/artfynd/A 25307-2025 artfynd.xlsx
+++ b/artfynd/A 25307-2025 artfynd.xlsx
@@ -819,7 +819,7 @@
         <v>126964623</v>
       </c>
       <c r="B3" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 25307-2025 artfynd.xlsx
+++ b/artfynd/A 25307-2025 artfynd.xlsx
@@ -819,7 +819,7 @@
         <v>126964623</v>
       </c>
       <c r="B3" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 25307-2025 artfynd.xlsx
+++ b/artfynd/A 25307-2025 artfynd.xlsx
@@ -819,7 +819,7 @@
         <v>126964623</v>
       </c>
       <c r="B3" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 25307-2025 artfynd.xlsx
+++ b/artfynd/A 25307-2025 artfynd.xlsx
@@ -819,7 +819,7 @@
         <v>126964623</v>
       </c>
       <c r="B3" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 25307-2025 artfynd.xlsx
+++ b/artfynd/A 25307-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,6 +911,3331 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>127843638</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98456</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Valasjö Södra, Forsed, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>625697</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6987735</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>127843624</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98456</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Valasjö Södra, Forsed, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>626591</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6987878</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127843629</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98456</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Valasjö Södra, Forsed, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>626614</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6987921</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127843632</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98456</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Valasjö Södra, Forsed, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>626585</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6987992</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127843626</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98456</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Valasjö Södra, Forsed, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>626538</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6987872</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>127843663</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79020</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Valasjö Södra, Forsed, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>626111</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6987829</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127843621</v>
+      </c>
+      <c r="B10" t="n">
+        <v>56855</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Valasjö Södra, Forsed, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>626166</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6987813</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hane + färsk spillning + fjädrar</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127843654</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79020</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Valasjö Södra, Forsed, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>626573</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6987922</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127843655</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79020</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Valasjö Södra, Forsed, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>626586</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6987934</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127843649</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79020</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Valasjö Södra, Forsed, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>626636</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6988002</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127843656</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79020</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Valasjö Södra, Forsed, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>626599</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6987942</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127843625</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98456</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Valasjön Södra, Forsed, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>626786</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6987870</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127843622</v>
+      </c>
+      <c r="B16" t="n">
+        <v>56855</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Valasjö Södra, Forsed, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>626173</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6987818</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Hona.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127843633</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98456</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Valasjö Södra, Forsed, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>625708</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6987784</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127843651</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79020</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Valasjö Södra, Forsed, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>626634</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6987851</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127843653</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79020</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Valasjö Södra, Forsed, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>626546</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6987888</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>127843647</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79020</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Valasjö Södra, Forsed, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>625782</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6987737</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>127843627</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98456</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Valasjö Södra, Forsed, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>626583</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6987883</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>127843658</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79020</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Valasjö Södra, Forsed, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>626608</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6988027</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>127843659</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79020</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Valasjö Södra, Forsed, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>626194</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6987835</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>127843665</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79020</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Valasjö Södra, Forsed, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>625632</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6987762</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>127843657</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79020</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Valasjö Södra, Forsed, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>626593</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6987973</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>127843664</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79020</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Valasjö Södra, Forsed, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>625703</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6987775</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>127843661</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79020</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Valasjö Södra, Forsed, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>626136</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6987811</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>127843640</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98456</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Valasjö Södra, Forsed, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>625714</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6987737</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>127843636</v>
+      </c>
+      <c r="B29" t="n">
+        <v>98456</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Valasjö Södra, Forsed, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>625562</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6987669</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>127843623</v>
+      </c>
+      <c r="B30" t="n">
+        <v>97333</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Valasjö Södra, Forsed, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>625778</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6987795</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>127843631</v>
+      </c>
+      <c r="B31" t="n">
+        <v>98456</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Valasjö Södra, Forsed, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>626615</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6987927</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>127843662</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79020</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Valasjö Södra, Forsed, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>626114</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6987818</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>127843660</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79020</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Valasjö Södra, Forsed, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>626158</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6987825</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>127843645</v>
+      </c>
+      <c r="B34" t="n">
+        <v>98456</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Valasjö Södra, Forsed, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>625763</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6987742</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>127843666</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79020</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Valasjö Södra, Forsed, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>625569</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6987664</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>127843630</v>
+      </c>
+      <c r="B36" t="n">
+        <v>98456</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Valasjö Södra, Forsed, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>626637</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6987919</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>127843628</v>
+      </c>
+      <c r="B37" t="n">
+        <v>98456</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Valasjö Södra, Forsed, Ång</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>626596</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6987884</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Elke Blöhbaum</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25307-2025 artfynd.xlsx
+++ b/artfynd/A 25307-2025 artfynd.xlsx
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127843638</v>
+        <v>127843624</v>
       </c>
       <c r="B4" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -941,17 +941,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Valasjö Södra, Forsed, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>625697</v>
+        <v>626591</v>
       </c>
       <c r="R4" t="n">
-        <v>6987735</v>
+        <v>6987878</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,12 +982,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -992,6 +996,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1010,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127843624</v>
+        <v>127843638</v>
       </c>
       <c r="B5" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1038,21 +1043,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Valasjö Södra, Forsed, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626591</v>
+        <v>625697</v>
       </c>
       <c r="R5" t="n">
-        <v>6987878</v>
+        <v>6987735</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,12 +1080,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,7 +1094,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1112,10 +1112,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127843629</v>
+        <v>127843626</v>
       </c>
       <c r="B6" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1147,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626614</v>
+        <v>626538</v>
       </c>
       <c r="R6" t="n">
-        <v>6987921</v>
+        <v>6987872</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,7 +1212,7 @@
         <v>127843632</v>
       </c>
       <c r="B7" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1306,10 +1306,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127843626</v>
+        <v>127843629</v>
       </c>
       <c r="B8" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626538</v>
+        <v>626614</v>
       </c>
       <c r="R8" t="n">
-        <v>6987872</v>
+        <v>6987921</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,7 +1406,7 @@
         <v>127843663</v>
       </c>
       <c r="B9" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>127843621</v>
       </c>
       <c r="B10" t="n">
-        <v>56855</v>
+        <v>56858</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>127843654</v>
       </c>
       <c r="B11" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>127843655</v>
       </c>
       <c r="B12" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1800,45 +1800,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127843649</v>
+        <v>127843625</v>
       </c>
       <c r="B13" t="n">
-        <v>79020</v>
+        <v>98459</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Valasjö Södra, Forsed, Ång</t>
+          <t>Valasjön Södra, Forsed, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626636</v>
+        <v>626786</v>
       </c>
       <c r="R13" t="n">
-        <v>6988002</v>
+        <v>6987870</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1897,10 +1897,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127843656</v>
+        <v>127843649</v>
       </c>
       <c r="B14" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626599</v>
+        <v>626636</v>
       </c>
       <c r="R14" t="n">
-        <v>6987942</v>
+        <v>6988002</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1994,45 +1994,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127843625</v>
+        <v>127843656</v>
       </c>
       <c r="B15" t="n">
-        <v>98456</v>
+        <v>79023</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Valasjön Södra, Forsed, Ång</t>
+          <t>Valasjö Södra, Forsed, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626786</v>
+        <v>626599</v>
       </c>
       <c r="R15" t="n">
-        <v>6987870</v>
+        <v>6987942</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2094,7 +2094,7 @@
         <v>127843622</v>
       </c>
       <c r="B16" t="n">
-        <v>56855</v>
+        <v>56858</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2201,32 +2201,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127843633</v>
+        <v>127843651</v>
       </c>
       <c r="B17" t="n">
-        <v>98456</v>
+        <v>79023</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2236,10 +2236,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>625708</v>
+        <v>626634</v>
       </c>
       <c r="R17" t="n">
-        <v>6987784</v>
+        <v>6987851</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2266,12 +2266,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2298,32 +2298,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127843651</v>
+        <v>127843633</v>
       </c>
       <c r="B18" t="n">
-        <v>79020</v>
+        <v>98459</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2333,10 +2333,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626634</v>
+        <v>625708</v>
       </c>
       <c r="R18" t="n">
-        <v>6987851</v>
+        <v>6987784</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2363,12 +2363,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2398,7 +2398,7 @@
         <v>127843653</v>
       </c>
       <c r="B19" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>127843647</v>
       </c>
       <c r="B20" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>127843627</v>
       </c>
       <c r="B21" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>127843658</v>
       </c>
       <c r="B22" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         <v>127843659</v>
       </c>
       <c r="B23" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         <v>127843665</v>
       </c>
       <c r="B24" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>127843657</v>
       </c>
       <c r="B25" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>127843664</v>
       </c>
       <c r="B26" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>127843661</v>
       </c>
       <c r="B27" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3268,32 +3268,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127843640</v>
+        <v>127843623</v>
       </c>
       <c r="B28" t="n">
-        <v>98456</v>
+        <v>97336</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3303,10 +3303,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>625714</v>
+        <v>625778</v>
       </c>
       <c r="R28" t="n">
-        <v>6987737</v>
+        <v>6987795</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3365,10 +3365,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127843636</v>
+        <v>127843640</v>
       </c>
       <c r="B29" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3400,10 +3400,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>625562</v>
+        <v>625714</v>
       </c>
       <c r="R29" t="n">
-        <v>6987669</v>
+        <v>6987737</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3462,32 +3462,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127843623</v>
+        <v>127843636</v>
       </c>
       <c r="B30" t="n">
-        <v>97333</v>
+        <v>98459</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3497,10 +3497,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>625778</v>
+        <v>625562</v>
       </c>
       <c r="R30" t="n">
-        <v>6987795</v>
+        <v>6987669</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3562,7 +3562,7 @@
         <v>127843631</v>
       </c>
       <c r="B31" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         <v>127843662</v>
       </c>
       <c r="B32" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>127843660</v>
       </c>
       <c r="B33" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>127843645</v>
       </c>
       <c r="B34" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>127843666</v>
       </c>
       <c r="B35" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>127843630</v>
       </c>
       <c r="B36" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         <v>127843628</v>
       </c>
       <c r="B37" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 25307-2025 artfynd.xlsx
+++ b/artfynd/A 25307-2025 artfynd.xlsx
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127843624</v>
+        <v>127843638</v>
       </c>
       <c r="B4" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -941,21 +941,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Valasjö Södra, Forsed, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626591</v>
+        <v>625697</v>
       </c>
       <c r="R4" t="n">
-        <v>6987878</v>
+        <v>6987735</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,12 +978,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +992,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1015,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127843638</v>
+        <v>127843624</v>
       </c>
       <c r="B5" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1043,17 +1038,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Valasjö Södra, Forsed, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>625697</v>
+        <v>626591</v>
       </c>
       <c r="R5" t="n">
-        <v>6987735</v>
+        <v>6987878</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,12 +1079,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1094,6 +1093,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1112,10 +1112,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127843626</v>
+        <v>127843629</v>
       </c>
       <c r="B6" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1147,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626538</v>
+        <v>626614</v>
       </c>
       <c r="R6" t="n">
-        <v>6987872</v>
+        <v>6987921</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,7 +1212,7 @@
         <v>127843632</v>
       </c>
       <c r="B7" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1306,10 +1306,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127843629</v>
+        <v>127843626</v>
       </c>
       <c r="B8" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626614</v>
+        <v>626538</v>
       </c>
       <c r="R8" t="n">
-        <v>6987921</v>
+        <v>6987872</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1406,7 +1406,7 @@
         <v>127843663</v>
       </c>
       <c r="B9" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>127843621</v>
       </c>
       <c r="B10" t="n">
-        <v>56858</v>
+        <v>56864</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,10 +1606,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127843654</v>
+        <v>127843655</v>
       </c>
       <c r="B11" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1641,10 +1641,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626573</v>
+        <v>626586</v>
       </c>
       <c r="R11" t="n">
-        <v>6987922</v>
+        <v>6987934</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1703,10 +1703,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127843655</v>
+        <v>127843654</v>
       </c>
       <c r="B12" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1738,10 +1738,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626586</v>
+        <v>626573</v>
       </c>
       <c r="R12" t="n">
-        <v>6987934</v>
+        <v>6987922</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1803,7 +1803,7 @@
         <v>127843625</v>
       </c>
       <c r="B13" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127843649</v>
+        <v>127843656</v>
       </c>
       <c r="B14" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626636</v>
+        <v>626599</v>
       </c>
       <c r="R14" t="n">
-        <v>6988002</v>
+        <v>6987942</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1994,10 +1994,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127843656</v>
+        <v>127843649</v>
       </c>
       <c r="B15" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2029,10 +2029,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626599</v>
+        <v>626636</v>
       </c>
       <c r="R15" t="n">
-        <v>6987942</v>
+        <v>6988002</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2094,7 +2094,7 @@
         <v>127843622</v>
       </c>
       <c r="B16" t="n">
-        <v>56858</v>
+        <v>56864</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>127843651</v>
       </c>
       <c r="B17" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>127843633</v>
       </c>
       <c r="B18" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>127843653</v>
       </c>
       <c r="B19" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>127843647</v>
       </c>
       <c r="B20" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>127843627</v>
       </c>
       <c r="B21" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>127843658</v>
       </c>
       <c r="B22" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         <v>127843659</v>
       </c>
       <c r="B23" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         <v>127843665</v>
       </c>
       <c r="B24" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>127843657</v>
       </c>
       <c r="B25" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>127843664</v>
       </c>
       <c r="B26" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>127843661</v>
       </c>
       <c r="B27" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3268,32 +3268,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127843623</v>
+        <v>127843640</v>
       </c>
       <c r="B28" t="n">
-        <v>97336</v>
+        <v>98467</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3303,10 +3303,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>625778</v>
+        <v>625714</v>
       </c>
       <c r="R28" t="n">
-        <v>6987795</v>
+        <v>6987737</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3365,10 +3365,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127843640</v>
+        <v>127843636</v>
       </c>
       <c r="B29" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3400,10 +3400,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>625714</v>
+        <v>625562</v>
       </c>
       <c r="R29" t="n">
-        <v>6987737</v>
+        <v>6987669</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3462,32 +3462,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127843636</v>
+        <v>127843623</v>
       </c>
       <c r="B30" t="n">
-        <v>98459</v>
+        <v>97344</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3497,10 +3497,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>625562</v>
+        <v>625778</v>
       </c>
       <c r="R30" t="n">
-        <v>6987669</v>
+        <v>6987795</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3562,7 +3562,7 @@
         <v>127843631</v>
       </c>
       <c r="B31" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         <v>127843662</v>
       </c>
       <c r="B32" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>127843660</v>
       </c>
       <c r="B33" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>127843645</v>
       </c>
       <c r="B34" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3947,32 +3947,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127843666</v>
+        <v>127843630</v>
       </c>
       <c r="B35" t="n">
-        <v>79023</v>
+        <v>98467</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3982,10 +3982,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>625569</v>
+        <v>626637</v>
       </c>
       <c r="R35" t="n">
-        <v>6987664</v>
+        <v>6987919</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4012,12 +4012,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4044,32 +4044,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127843630</v>
+        <v>127843666</v>
       </c>
       <c r="B36" t="n">
-        <v>98459</v>
+        <v>79029</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4079,10 +4079,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>626637</v>
+        <v>625569</v>
       </c>
       <c r="R36" t="n">
-        <v>6987919</v>
+        <v>6987664</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4109,12 +4109,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4144,7 +4144,7 @@
         <v>127843628</v>
       </c>
       <c r="B37" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 25307-2025 artfynd.xlsx
+++ b/artfynd/A 25307-2025 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>127843638</v>
       </c>
       <c r="B4" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>127843624</v>
       </c>
       <c r="B5" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>127843629</v>
       </c>
       <c r="B6" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>127843632</v>
       </c>
       <c r="B7" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>127843626</v>
       </c>
       <c r="B8" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127843655</v>
+        <v>127843654</v>
       </c>
       <c r="B11" t="n">
         <v>79029</v>
@@ -1641,10 +1641,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626586</v>
+        <v>626573</v>
       </c>
       <c r="R11" t="n">
-        <v>6987934</v>
+        <v>6987922</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1703,7 +1703,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127843654</v>
+        <v>127843655</v>
       </c>
       <c r="B12" t="n">
         <v>79029</v>
@@ -1738,10 +1738,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626573</v>
+        <v>626586</v>
       </c>
       <c r="R12" t="n">
-        <v>6987922</v>
+        <v>6987934</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1800,45 +1800,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127843625</v>
+        <v>127843649</v>
       </c>
       <c r="B13" t="n">
-        <v>98467</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Valasjön Södra, Forsed, Ång</t>
+          <t>Valasjö Södra, Forsed, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626786</v>
+        <v>626636</v>
       </c>
       <c r="R13" t="n">
-        <v>6987870</v>
+        <v>6988002</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1994,45 +1994,53 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127843649</v>
+        <v>127843622</v>
       </c>
       <c r="B15" t="n">
-        <v>79029</v>
+        <v>56864</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Valasjö Södra, Forsed, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626636</v>
+        <v>626173</v>
       </c>
       <c r="R15" t="n">
-        <v>6988002</v>
+        <v>6987818</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2059,12 +2067,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Hona.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2091,53 +2104,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127843622</v>
+        <v>127843625</v>
       </c>
       <c r="B16" t="n">
-        <v>56864</v>
+        <v>98468</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Valasjö Södra, Forsed, Ång</t>
+          <t>Valasjön Södra, Forsed, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626173</v>
+        <v>626786</v>
       </c>
       <c r="R16" t="n">
-        <v>6987818</v>
+        <v>6987870</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2164,17 +2169,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Hona.</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2301,7 +2301,7 @@
         <v>127843633</v>
       </c>
       <c r="B18" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>127843627</v>
       </c>
       <c r="B21" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>127843640</v>
       </c>
       <c r="B28" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>127843636</v>
       </c>
       <c r="B29" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>127843623</v>
       </c>
       <c r="B30" t="n">
-        <v>97344</v>
+        <v>97345</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>127843631</v>
       </c>
       <c r="B31" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>127843645</v>
       </c>
       <c r="B34" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3947,32 +3947,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127843630</v>
+        <v>127843666</v>
       </c>
       <c r="B35" t="n">
-        <v>98467</v>
+        <v>79029</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3982,10 +3982,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>626637</v>
+        <v>625569</v>
       </c>
       <c r="R35" t="n">
-        <v>6987919</v>
+        <v>6987664</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4012,12 +4012,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4044,32 +4044,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127843666</v>
+        <v>127843630</v>
       </c>
       <c r="B36" t="n">
-        <v>79029</v>
+        <v>98468</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4079,10 +4079,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>625569</v>
+        <v>626637</v>
       </c>
       <c r="R36" t="n">
-        <v>6987664</v>
+        <v>6987919</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4109,12 +4109,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4144,7 +4144,7 @@
         <v>127843628</v>
       </c>
       <c r="B37" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 25307-2025 artfynd.xlsx
+++ b/artfynd/A 25307-2025 artfynd.xlsx
@@ -913,7 +913,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127843638</v>
+        <v>127843624</v>
       </c>
       <c r="B4" t="n">
         <v>98468</v>
@@ -941,17 +941,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Valasjö Södra, Forsed, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>625697</v>
+        <v>626591</v>
       </c>
       <c r="R4" t="n">
-        <v>6987735</v>
+        <v>6987878</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,12 +982,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -992,6 +996,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1010,7 +1015,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127843624</v>
+        <v>127843638</v>
       </c>
       <c r="B5" t="n">
         <v>98468</v>
@@ -1038,21 +1043,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Valasjö Södra, Forsed, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626591</v>
+        <v>625697</v>
       </c>
       <c r="R5" t="n">
-        <v>6987878</v>
+        <v>6987735</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,12 +1080,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,7 +1094,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1112,7 +1112,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127843629</v>
+        <v>127843626</v>
       </c>
       <c r="B6" t="n">
         <v>98468</v>
@@ -1147,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626614</v>
+        <v>626538</v>
       </c>
       <c r="R6" t="n">
-        <v>6987921</v>
+        <v>6987872</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1306,7 +1306,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127843626</v>
+        <v>127843629</v>
       </c>
       <c r="B8" t="n">
         <v>98468</v>
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626538</v>
+        <v>626614</v>
       </c>
       <c r="R8" t="n">
-        <v>6987872</v>
+        <v>6987921</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1403,45 +1403,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127843663</v>
+        <v>127843621</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>56864</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Valasjö Södra, Forsed, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626111</v>
+        <v>626166</v>
       </c>
       <c r="R9" t="n">
-        <v>6987829</v>
+        <v>6987813</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1474,6 +1478,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Hane + färsk spillning + fjädrar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1500,49 +1509,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127843621</v>
+        <v>127843663</v>
       </c>
       <c r="B10" t="n">
-        <v>56864</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Valasjö Södra, Forsed, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626166</v>
+        <v>626111</v>
       </c>
       <c r="R10" t="n">
-        <v>6987813</v>
+        <v>6987829</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1575,11 +1580,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-23</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Hane + färsk spillning + fjädrar</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 25307-2025 artfynd.xlsx
+++ b/artfynd/A 25307-2025 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>127843624</v>
       </c>
       <c r="B4" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>127843638</v>
       </c>
       <c r="B5" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>127843626</v>
       </c>
       <c r="B6" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>127843632</v>
       </c>
       <c r="B7" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>127843629</v>
       </c>
       <c r="B8" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1403,49 +1403,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127843621</v>
+        <v>127843663</v>
       </c>
       <c r="B9" t="n">
-        <v>56864</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Valasjö Södra, Forsed, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626166</v>
+        <v>626111</v>
       </c>
       <c r="R9" t="n">
-        <v>6987813</v>
+        <v>6987829</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1478,11 +1474,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-23</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Hane + färsk spillning + fjädrar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1509,45 +1500,49 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127843663</v>
+        <v>127843621</v>
       </c>
       <c r="B10" t="n">
-        <v>79029</v>
+        <v>56864</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Valasjö Södra, Forsed, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626111</v>
+        <v>626166</v>
       </c>
       <c r="R10" t="n">
-        <v>6987829</v>
+        <v>6987813</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1580,6 +1575,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hane + färsk spillning + fjädrar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2107,7 +2107,7 @@
         <v>127843625</v>
       </c>
       <c r="B16" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>127843633</v>
       </c>
       <c r="B18" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>127843627</v>
       </c>
       <c r="B21" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>127843640</v>
       </c>
       <c r="B28" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>127843636</v>
       </c>
       <c r="B29" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>127843623</v>
       </c>
       <c r="B30" t="n">
-        <v>97345</v>
+        <v>97346</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>127843631</v>
       </c>
       <c r="B31" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>127843645</v>
       </c>
       <c r="B34" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3947,32 +3947,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127843666</v>
+        <v>127843630</v>
       </c>
       <c r="B35" t="n">
-        <v>79029</v>
+        <v>98469</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3982,10 +3982,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>625569</v>
+        <v>626637</v>
       </c>
       <c r="R35" t="n">
-        <v>6987664</v>
+        <v>6987919</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4012,12 +4012,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4044,32 +4044,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127843630</v>
+        <v>127843666</v>
       </c>
       <c r="B36" t="n">
-        <v>98468</v>
+        <v>79029</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4079,10 +4079,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>626637</v>
+        <v>625569</v>
       </c>
       <c r="R36" t="n">
-        <v>6987919</v>
+        <v>6987664</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4109,12 +4109,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4144,7 +4144,7 @@
         <v>127843628</v>
       </c>
       <c r="B37" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 25307-2025 artfynd.xlsx
+++ b/artfynd/A 25307-2025 artfynd.xlsx
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127843624</v>
+        <v>127843632</v>
       </c>
       <c r="B4" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -941,21 +941,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Valasjö Södra, Forsed, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626591</v>
+        <v>626585</v>
       </c>
       <c r="R4" t="n">
-        <v>6987878</v>
+        <v>6987992</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +992,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1015,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127843638</v>
+        <v>127843629</v>
       </c>
       <c r="B5" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1050,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>625697</v>
+        <v>626614</v>
       </c>
       <c r="R5" t="n">
-        <v>6987735</v>
+        <v>6987921</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,12 +1075,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127843626</v>
+        <v>127843638</v>
       </c>
       <c r="B6" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1147,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626538</v>
+        <v>625697</v>
       </c>
       <c r="R6" t="n">
-        <v>6987872</v>
+        <v>6987735</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1177,12 +1172,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1209,10 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127843632</v>
+        <v>127843624</v>
       </c>
       <c r="B7" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1237,17 +1232,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Valasjö Södra, Forsed, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626585</v>
+        <v>626591</v>
       </c>
       <c r="R7" t="n">
-        <v>6987992</v>
+        <v>6987878</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1288,6 +1287,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1306,10 +1306,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127843629</v>
+        <v>127843626</v>
       </c>
       <c r="B8" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626614</v>
+        <v>626538</v>
       </c>
       <c r="R8" t="n">
-        <v>6987921</v>
+        <v>6987872</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1800,45 +1800,53 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127843649</v>
+        <v>127843622</v>
       </c>
       <c r="B13" t="n">
-        <v>79029</v>
+        <v>56864</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Valasjö Södra, Forsed, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626636</v>
+        <v>626173</v>
       </c>
       <c r="R13" t="n">
-        <v>6988002</v>
+        <v>6987818</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1865,12 +1873,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Hona.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1897,45 +1910,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127843656</v>
+        <v>127843625</v>
       </c>
       <c r="B14" t="n">
-        <v>79029</v>
+        <v>98470</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Valasjö Södra, Forsed, Ång</t>
+          <t>Valasjön Södra, Forsed, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626599</v>
+        <v>626786</v>
       </c>
       <c r="R14" t="n">
-        <v>6987942</v>
+        <v>6987870</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1994,53 +2007,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127843622</v>
+        <v>127843649</v>
       </c>
       <c r="B15" t="n">
-        <v>56864</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Valasjö Södra, Forsed, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626173</v>
+        <v>626636</v>
       </c>
       <c r="R15" t="n">
-        <v>6987818</v>
+        <v>6988002</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2067,17 +2072,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Hona.</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2104,45 +2104,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127843625</v>
+        <v>127843656</v>
       </c>
       <c r="B16" t="n">
-        <v>98469</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Valasjön Södra, Forsed, Ång</t>
+          <t>Valasjö Södra, Forsed, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626786</v>
+        <v>626599</v>
       </c>
       <c r="R16" t="n">
-        <v>6987870</v>
+        <v>6987942</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2201,32 +2201,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127843651</v>
+        <v>127843633</v>
       </c>
       <c r="B17" t="n">
-        <v>79029</v>
+        <v>98470</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2236,10 +2236,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626634</v>
+        <v>625708</v>
       </c>
       <c r="R17" t="n">
-        <v>6987851</v>
+        <v>6987784</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2266,12 +2266,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2298,32 +2298,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127843633</v>
+        <v>127843651</v>
       </c>
       <c r="B18" t="n">
-        <v>98469</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2333,10 +2333,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>625708</v>
+        <v>626634</v>
       </c>
       <c r="R18" t="n">
-        <v>6987784</v>
+        <v>6987851</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2363,12 +2363,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2592,7 +2592,7 @@
         <v>127843627</v>
       </c>
       <c r="B21" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>127843640</v>
       </c>
       <c r="B28" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>127843636</v>
       </c>
       <c r="B29" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>127843623</v>
       </c>
       <c r="B30" t="n">
-        <v>97346</v>
+        <v>97347</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>127843631</v>
       </c>
       <c r="B31" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>127843645</v>
       </c>
       <c r="B34" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3947,32 +3947,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127843630</v>
+        <v>127843666</v>
       </c>
       <c r="B35" t="n">
-        <v>98469</v>
+        <v>79029</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3982,10 +3982,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>626637</v>
+        <v>625569</v>
       </c>
       <c r="R35" t="n">
-        <v>6987919</v>
+        <v>6987664</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4012,12 +4012,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4044,32 +4044,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127843666</v>
+        <v>127843630</v>
       </c>
       <c r="B36" t="n">
-        <v>79029</v>
+        <v>98470</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4079,10 +4079,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>625569</v>
+        <v>626637</v>
       </c>
       <c r="R36" t="n">
-        <v>6987664</v>
+        <v>6987919</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4109,12 +4109,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4144,7 +4144,7 @@
         <v>127843628</v>
       </c>
       <c r="B37" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 25307-2025 artfynd.xlsx
+++ b/artfynd/A 25307-2025 artfynd.xlsx
@@ -913,7 +913,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127843632</v>
+        <v>127843638</v>
       </c>
       <c r="B4" t="n">
         <v>98470</v>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626585</v>
+        <v>625697</v>
       </c>
       <c r="R4" t="n">
-        <v>6987992</v>
+        <v>6987735</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,12 +978,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,7 +1010,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127843629</v>
+        <v>127843624</v>
       </c>
       <c r="B5" t="n">
         <v>98470</v>
@@ -1038,17 +1038,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Valasjö Södra, Forsed, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626614</v>
+        <v>626591</v>
       </c>
       <c r="R5" t="n">
-        <v>6987921</v>
+        <v>6987878</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,6 +1093,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1107,7 +1112,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127843638</v>
+        <v>127843629</v>
       </c>
       <c r="B6" t="n">
         <v>98470</v>
@@ -1142,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>625697</v>
+        <v>626614</v>
       </c>
       <c r="R6" t="n">
-        <v>6987735</v>
+        <v>6987921</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1172,12 +1177,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1204,7 +1209,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127843624</v>
+        <v>127843632</v>
       </c>
       <c r="B7" t="n">
         <v>98470</v>
@@ -1232,21 +1237,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Valasjö Södra, Forsed, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626591</v>
+        <v>626585</v>
       </c>
       <c r="R7" t="n">
-        <v>6987878</v>
+        <v>6987992</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,7 +1288,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1606,7 +1606,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127843654</v>
+        <v>127843655</v>
       </c>
       <c r="B11" t="n">
         <v>79029</v>
@@ -1641,10 +1641,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626573</v>
+        <v>626586</v>
       </c>
       <c r="R11" t="n">
-        <v>6987922</v>
+        <v>6987934</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1703,7 +1703,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127843655</v>
+        <v>127843654</v>
       </c>
       <c r="B12" t="n">
         <v>79029</v>
@@ -1738,10 +1738,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626586</v>
+        <v>626573</v>
       </c>
       <c r="R12" t="n">
-        <v>6987934</v>
+        <v>6987922</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1800,53 +1800,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127843622</v>
+        <v>127843625</v>
       </c>
       <c r="B13" t="n">
-        <v>56864</v>
+        <v>98470</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Valasjö Södra, Forsed, Ång</t>
+          <t>Valasjön Södra, Forsed, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626173</v>
+        <v>626786</v>
       </c>
       <c r="R13" t="n">
-        <v>6987818</v>
+        <v>6987870</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1873,17 +1865,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Hona.</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1910,45 +1897,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127843625</v>
+        <v>127843656</v>
       </c>
       <c r="B14" t="n">
-        <v>98470</v>
+        <v>79029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Valasjön Södra, Forsed, Ång</t>
+          <t>Valasjö Södra, Forsed, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626786</v>
+        <v>626599</v>
       </c>
       <c r="R14" t="n">
-        <v>6987870</v>
+        <v>6987942</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2104,45 +2091,53 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127843656</v>
+        <v>127843622</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>56864</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Valasjö Södra, Forsed, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626599</v>
+        <v>626173</v>
       </c>
       <c r="R16" t="n">
-        <v>6987942</v>
+        <v>6987818</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2169,12 +2164,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Hona.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2201,32 +2201,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127843633</v>
+        <v>127843651</v>
       </c>
       <c r="B17" t="n">
-        <v>98470</v>
+        <v>79029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2236,10 +2236,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>625708</v>
+        <v>626634</v>
       </c>
       <c r="R17" t="n">
-        <v>6987784</v>
+        <v>6987851</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2266,12 +2266,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2298,32 +2298,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127843651</v>
+        <v>127843633</v>
       </c>
       <c r="B18" t="n">
-        <v>79029</v>
+        <v>98470</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2333,10 +2333,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626634</v>
+        <v>625708</v>
       </c>
       <c r="R18" t="n">
-        <v>6987851</v>
+        <v>6987784</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2363,12 +2363,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 25307-2025 artfynd.xlsx
+++ b/artfynd/A 25307-2025 artfynd.xlsx
@@ -1800,45 +1800,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127843625</v>
+        <v>127843656</v>
       </c>
       <c r="B13" t="n">
-        <v>98470</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Valasjön Södra, Forsed, Ång</t>
+          <t>Valasjö Södra, Forsed, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626786</v>
+        <v>626599</v>
       </c>
       <c r="R13" t="n">
-        <v>6987870</v>
+        <v>6987942</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1897,7 +1897,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127843656</v>
+        <v>127843649</v>
       </c>
       <c r="B14" t="n">
         <v>79029</v>
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626599</v>
+        <v>626636</v>
       </c>
       <c r="R14" t="n">
-        <v>6987942</v>
+        <v>6988002</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1994,45 +1994,53 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127843649</v>
+        <v>127843622</v>
       </c>
       <c r="B15" t="n">
-        <v>79029</v>
+        <v>56864</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Valasjö Södra, Forsed, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626636</v>
+        <v>626173</v>
       </c>
       <c r="R15" t="n">
-        <v>6988002</v>
+        <v>6987818</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2059,12 +2067,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Hona.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2091,53 +2104,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127843622</v>
+        <v>127843625</v>
       </c>
       <c r="B16" t="n">
-        <v>56864</v>
+        <v>98470</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Valasjö Södra, Forsed, Ång</t>
+          <t>Valasjön Södra, Forsed, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626173</v>
+        <v>626786</v>
       </c>
       <c r="R16" t="n">
-        <v>6987818</v>
+        <v>6987870</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2164,17 +2169,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Hona.</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 25307-2025 artfynd.xlsx
+++ b/artfynd/A 25307-2025 artfynd.xlsx
@@ -1403,45 +1403,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127843663</v>
+        <v>127843621</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>56864</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Valasjö Södra, Forsed, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626111</v>
+        <v>626166</v>
       </c>
       <c r="R9" t="n">
-        <v>6987829</v>
+        <v>6987813</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1474,6 +1478,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Hane + färsk spillning + fjädrar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1500,49 +1509,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127843621</v>
+        <v>127843663</v>
       </c>
       <c r="B10" t="n">
-        <v>56864</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Valasjö Södra, Forsed, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626166</v>
+        <v>626111</v>
       </c>
       <c r="R10" t="n">
-        <v>6987813</v>
+        <v>6987829</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1575,11 +1580,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-23</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Hane + färsk spillning + fjädrar</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 25307-2025 artfynd.xlsx
+++ b/artfynd/A 25307-2025 artfynd.xlsx
@@ -1403,49 +1403,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127843621</v>
+        <v>127843663</v>
       </c>
       <c r="B9" t="n">
-        <v>56864</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Valasjö Södra, Forsed, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626166</v>
+        <v>626111</v>
       </c>
       <c r="R9" t="n">
-        <v>6987813</v>
+        <v>6987829</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1478,11 +1474,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-23</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Hane + färsk spillning + fjädrar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1509,45 +1500,49 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127843663</v>
+        <v>127843621</v>
       </c>
       <c r="B10" t="n">
-        <v>79029</v>
+        <v>56864</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Valasjö Södra, Forsed, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626111</v>
+        <v>626166</v>
       </c>
       <c r="R10" t="n">
-        <v>6987829</v>
+        <v>6987813</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1580,6 +1575,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hane + färsk spillning + fjädrar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1800,45 +1800,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127843656</v>
+        <v>127843625</v>
       </c>
       <c r="B13" t="n">
-        <v>79029</v>
+        <v>98470</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Valasjö Södra, Forsed, Ång</t>
+          <t>Valasjön Södra, Forsed, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626599</v>
+        <v>626786</v>
       </c>
       <c r="R13" t="n">
-        <v>6987942</v>
+        <v>6987870</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1897,7 +1897,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127843649</v>
+        <v>127843656</v>
       </c>
       <c r="B14" t="n">
         <v>79029</v>
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626636</v>
+        <v>626599</v>
       </c>
       <c r="R14" t="n">
-        <v>6988002</v>
+        <v>6987942</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1994,53 +1994,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127843622</v>
+        <v>127843649</v>
       </c>
       <c r="B15" t="n">
-        <v>56864</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Valasjö Södra, Forsed, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626173</v>
+        <v>626636</v>
       </c>
       <c r="R15" t="n">
-        <v>6987818</v>
+        <v>6988002</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2067,17 +2059,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Hona.</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2104,45 +2091,53 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127843625</v>
+        <v>127843622</v>
       </c>
       <c r="B16" t="n">
-        <v>98470</v>
+        <v>56864</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Valasjön Södra, Forsed, Ång</t>
+          <t>Valasjö Södra, Forsed, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626786</v>
+        <v>626173</v>
       </c>
       <c r="R16" t="n">
-        <v>6987870</v>
+        <v>6987818</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2169,12 +2164,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Hona.</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 25307-2025 artfynd.xlsx
+++ b/artfynd/A 25307-2025 artfynd.xlsx
@@ -1403,45 +1403,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127843663</v>
+        <v>127843621</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>56864</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Valasjö Södra, Forsed, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626111</v>
+        <v>626166</v>
       </c>
       <c r="R9" t="n">
-        <v>6987829</v>
+        <v>6987813</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1474,6 +1478,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Hane + färsk spillning + fjädrar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1500,49 +1509,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127843621</v>
+        <v>127843663</v>
       </c>
       <c r="B10" t="n">
-        <v>56864</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Valasjö Södra, Forsed, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626166</v>
+        <v>626111</v>
       </c>
       <c r="R10" t="n">
-        <v>6987813</v>
+        <v>6987829</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1575,11 +1580,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-23</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Hane + färsk spillning + fjädrar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1800,45 +1800,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127843625</v>
+        <v>127843656</v>
       </c>
       <c r="B13" t="n">
-        <v>98470</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Valasjön Södra, Forsed, Ång</t>
+          <t>Valasjö Södra, Forsed, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626786</v>
+        <v>626599</v>
       </c>
       <c r="R13" t="n">
-        <v>6987870</v>
+        <v>6987942</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1897,7 +1897,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127843656</v>
+        <v>127843649</v>
       </c>
       <c r="B14" t="n">
         <v>79029</v>
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626599</v>
+        <v>626636</v>
       </c>
       <c r="R14" t="n">
-        <v>6987942</v>
+        <v>6988002</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1994,45 +1994,53 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127843649</v>
+        <v>127843622</v>
       </c>
       <c r="B15" t="n">
-        <v>79029</v>
+        <v>56864</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Valasjö Södra, Forsed, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626636</v>
+        <v>626173</v>
       </c>
       <c r="R15" t="n">
-        <v>6988002</v>
+        <v>6987818</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2059,12 +2067,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Hona.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2091,53 +2104,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127843622</v>
+        <v>127843625</v>
       </c>
       <c r="B16" t="n">
-        <v>56864</v>
+        <v>98470</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Valasjö Södra, Forsed, Ång</t>
+          <t>Valasjön Södra, Forsed, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626173</v>
+        <v>626786</v>
       </c>
       <c r="R16" t="n">
-        <v>6987818</v>
+        <v>6987870</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2164,17 +2169,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Hona.</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 25307-2025 artfynd.xlsx
+++ b/artfynd/A 25307-2025 artfynd.xlsx
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127843638</v>
+        <v>127843624</v>
       </c>
       <c r="B4" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -941,17 +941,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Valasjö Södra, Forsed, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>625697</v>
+        <v>626591</v>
       </c>
       <c r="R4" t="n">
-        <v>6987735</v>
+        <v>6987878</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,12 +982,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -992,6 +996,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1010,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127843624</v>
+        <v>127843638</v>
       </c>
       <c r="B5" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1038,21 +1043,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Valasjö Södra, Forsed, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626591</v>
+        <v>625697</v>
       </c>
       <c r="R5" t="n">
-        <v>6987878</v>
+        <v>6987735</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,12 +1080,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,7 +1094,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1112,10 +1112,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127843629</v>
+        <v>127843626</v>
       </c>
       <c r="B6" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1147,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626614</v>
+        <v>626538</v>
       </c>
       <c r="R6" t="n">
-        <v>6987921</v>
+        <v>6987872</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,7 +1212,7 @@
         <v>127843632</v>
       </c>
       <c r="B7" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1306,10 +1306,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127843626</v>
+        <v>127843629</v>
       </c>
       <c r="B8" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626538</v>
+        <v>626614</v>
       </c>
       <c r="R8" t="n">
-        <v>6987872</v>
+        <v>6987921</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1512,7 +1512,7 @@
         <v>127843663</v>
       </c>
       <c r="B10" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1606,10 +1606,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127843655</v>
+        <v>127843654</v>
       </c>
       <c r="B11" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1641,10 +1641,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626586</v>
+        <v>626573</v>
       </c>
       <c r="R11" t="n">
-        <v>6987934</v>
+        <v>6987922</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1703,10 +1703,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127843654</v>
+        <v>127843655</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1738,10 +1738,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626573</v>
+        <v>626586</v>
       </c>
       <c r="R12" t="n">
-        <v>6987922</v>
+        <v>6987934</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1800,10 +1800,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127843656</v>
+        <v>127843649</v>
       </c>
       <c r="B13" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626599</v>
+        <v>626636</v>
       </c>
       <c r="R13" t="n">
-        <v>6987942</v>
+        <v>6988002</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1897,10 +1897,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127843649</v>
+        <v>127843656</v>
       </c>
       <c r="B14" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626636</v>
+        <v>626599</v>
       </c>
       <c r="R14" t="n">
-        <v>6988002</v>
+        <v>6987942</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2107,7 +2107,7 @@
         <v>127843625</v>
       </c>
       <c r="B16" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>127843651</v>
       </c>
       <c r="B17" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>127843633</v>
       </c>
       <c r="B18" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>127843653</v>
       </c>
       <c r="B19" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>127843647</v>
       </c>
       <c r="B20" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>127843627</v>
       </c>
       <c r="B21" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>127843658</v>
       </c>
       <c r="B22" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         <v>127843659</v>
       </c>
       <c r="B23" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         <v>127843665</v>
       </c>
       <c r="B24" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>127843657</v>
       </c>
       <c r="B25" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>127843664</v>
       </c>
       <c r="B26" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>127843661</v>
       </c>
       <c r="B27" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3268,32 +3268,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127843640</v>
+        <v>127843623</v>
       </c>
       <c r="B28" t="n">
-        <v>98470</v>
+        <v>97355</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3303,10 +3303,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>625714</v>
+        <v>625778</v>
       </c>
       <c r="R28" t="n">
-        <v>6987737</v>
+        <v>6987795</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3365,10 +3365,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127843636</v>
+        <v>127843640</v>
       </c>
       <c r="B29" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3400,10 +3400,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>625562</v>
+        <v>625714</v>
       </c>
       <c r="R29" t="n">
-        <v>6987669</v>
+        <v>6987737</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3462,32 +3462,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127843623</v>
+        <v>127843636</v>
       </c>
       <c r="B30" t="n">
-        <v>97347</v>
+        <v>98478</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3497,10 +3497,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>625778</v>
+        <v>625562</v>
       </c>
       <c r="R30" t="n">
-        <v>6987795</v>
+        <v>6987669</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3562,7 +3562,7 @@
         <v>127843631</v>
       </c>
       <c r="B31" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         <v>127843662</v>
       </c>
       <c r="B32" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>127843660</v>
       </c>
       <c r="B33" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>127843645</v>
       </c>
       <c r="B34" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>127843666</v>
       </c>
       <c r="B35" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>127843630</v>
       </c>
       <c r="B36" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         <v>127843628</v>
       </c>
       <c r="B37" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 25307-2025 artfynd.xlsx
+++ b/artfynd/A 25307-2025 artfynd.xlsx
@@ -2492,32 +2492,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127843647</v>
+        <v>127843627</v>
       </c>
       <c r="B20" t="n">
-        <v>79032</v>
+        <v>98478</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2527,10 +2527,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>625782</v>
+        <v>626583</v>
       </c>
       <c r="R20" t="n">
-        <v>6987737</v>
+        <v>6987883</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2589,32 +2589,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127843627</v>
+        <v>127843647</v>
       </c>
       <c r="B21" t="n">
-        <v>98478</v>
+        <v>79032</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>626583</v>
+        <v>625782</v>
       </c>
       <c r="R21" t="n">
-        <v>6987883</v>
+        <v>6987737</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2654,12 +2654,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 25307-2025 artfynd.xlsx
+++ b/artfynd/A 25307-2025 artfynd.xlsx
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127843624</v>
+        <v>127843638</v>
       </c>
       <c r="B4" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -941,21 +941,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Valasjö Södra, Forsed, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626591</v>
+        <v>625697</v>
       </c>
       <c r="R4" t="n">
-        <v>6987878</v>
+        <v>6987735</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,12 +978,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +992,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1015,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127843638</v>
+        <v>127843624</v>
       </c>
       <c r="B5" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1043,17 +1038,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Valasjö Södra, Forsed, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>625697</v>
+        <v>626591</v>
       </c>
       <c r="R5" t="n">
-        <v>6987735</v>
+        <v>6987878</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,12 +1079,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1094,6 +1093,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1112,10 +1112,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127843626</v>
+        <v>127843629</v>
       </c>
       <c r="B6" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1147,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626538</v>
+        <v>626614</v>
       </c>
       <c r="R6" t="n">
-        <v>6987872</v>
+        <v>6987921</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,7 +1212,7 @@
         <v>127843632</v>
       </c>
       <c r="B7" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1306,10 +1306,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127843629</v>
+        <v>127843626</v>
       </c>
       <c r="B8" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626614</v>
+        <v>626538</v>
       </c>
       <c r="R8" t="n">
-        <v>6987921</v>
+        <v>6987872</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1403,49 +1403,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127843621</v>
+        <v>127843663</v>
       </c>
       <c r="B9" t="n">
-        <v>56864</v>
+        <v>79083</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Valasjö Södra, Forsed, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626166</v>
+        <v>626111</v>
       </c>
       <c r="R9" t="n">
-        <v>6987813</v>
+        <v>6987829</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1478,11 +1474,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-23</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Hane + färsk spillning + fjädrar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1509,45 +1500,49 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127843663</v>
+        <v>127843621</v>
       </c>
       <c r="B10" t="n">
-        <v>79032</v>
+        <v>56876</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Valasjö Södra, Forsed, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626111</v>
+        <v>626166</v>
       </c>
       <c r="R10" t="n">
-        <v>6987829</v>
+        <v>6987813</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1580,6 +1575,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hane + färsk spillning + fjädrar</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1609,7 +1609,7 @@
         <v>127843654</v>
       </c>
       <c r="B11" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>127843655</v>
       </c>
       <c r="B12" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1800,45 +1800,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127843649</v>
+        <v>127843625</v>
       </c>
       <c r="B13" t="n">
-        <v>79032</v>
+        <v>98571</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Valasjö Södra, Forsed, Ång</t>
+          <t>Valasjön Södra, Forsed, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626636</v>
+        <v>626786</v>
       </c>
       <c r="R13" t="n">
-        <v>6988002</v>
+        <v>6987870</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1897,10 +1897,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127843656</v>
+        <v>127843649</v>
       </c>
       <c r="B14" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626599</v>
+        <v>626636</v>
       </c>
       <c r="R14" t="n">
-        <v>6987942</v>
+        <v>6988002</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1994,53 +1994,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127843622</v>
+        <v>127843656</v>
       </c>
       <c r="B15" t="n">
-        <v>56864</v>
+        <v>79083</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Valasjö Södra, Forsed, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626173</v>
+        <v>626599</v>
       </c>
       <c r="R15" t="n">
-        <v>6987818</v>
+        <v>6987942</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2067,17 +2059,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Hona.</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2104,45 +2091,53 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127843625</v>
+        <v>127843622</v>
       </c>
       <c r="B16" t="n">
-        <v>98478</v>
+        <v>56876</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Valasjön Södra, Forsed, Ång</t>
+          <t>Valasjö Södra, Forsed, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626786</v>
+        <v>626173</v>
       </c>
       <c r="R16" t="n">
-        <v>6987870</v>
+        <v>6987818</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2169,12 +2164,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Hona.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2201,32 +2201,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127843651</v>
+        <v>127843633</v>
       </c>
       <c r="B17" t="n">
-        <v>79032</v>
+        <v>98571</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2236,10 +2236,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626634</v>
+        <v>625708</v>
       </c>
       <c r="R17" t="n">
-        <v>6987851</v>
+        <v>6987784</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2266,12 +2266,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2298,32 +2298,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127843633</v>
+        <v>127843651</v>
       </c>
       <c r="B18" t="n">
-        <v>98478</v>
+        <v>79083</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2333,10 +2333,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>625708</v>
+        <v>626634</v>
       </c>
       <c r="R18" t="n">
-        <v>6987784</v>
+        <v>6987851</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2363,12 +2363,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2398,7 +2398,7 @@
         <v>127843653</v>
       </c>
       <c r="B19" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2492,32 +2492,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127843627</v>
+        <v>127843647</v>
       </c>
       <c r="B20" t="n">
-        <v>98478</v>
+        <v>79083</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2527,10 +2527,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626583</v>
+        <v>625782</v>
       </c>
       <c r="R20" t="n">
-        <v>6987883</v>
+        <v>6987737</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2589,32 +2589,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127843647</v>
+        <v>127843627</v>
       </c>
       <c r="B21" t="n">
-        <v>79032</v>
+        <v>98571</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>625782</v>
+        <v>626583</v>
       </c>
       <c r="R21" t="n">
-        <v>6987737</v>
+        <v>6987883</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2654,12 +2654,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2689,7 +2689,7 @@
         <v>127843658</v>
       </c>
       <c r="B22" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         <v>127843659</v>
       </c>
       <c r="B23" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         <v>127843665</v>
       </c>
       <c r="B24" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>127843657</v>
       </c>
       <c r="B25" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>127843664</v>
       </c>
       <c r="B26" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>127843661</v>
       </c>
       <c r="B27" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3268,32 +3268,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127843623</v>
+        <v>127843640</v>
       </c>
       <c r="B28" t="n">
-        <v>97355</v>
+        <v>98571</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3303,10 +3303,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>625778</v>
+        <v>625714</v>
       </c>
       <c r="R28" t="n">
-        <v>6987795</v>
+        <v>6987737</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3365,10 +3365,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127843640</v>
+        <v>127843636</v>
       </c>
       <c r="B29" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3400,10 +3400,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>625714</v>
+        <v>625562</v>
       </c>
       <c r="R29" t="n">
-        <v>6987737</v>
+        <v>6987669</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3462,32 +3462,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127843636</v>
+        <v>127843623</v>
       </c>
       <c r="B30" t="n">
-        <v>98478</v>
+        <v>97448</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3497,10 +3497,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>625562</v>
+        <v>625778</v>
       </c>
       <c r="R30" t="n">
-        <v>6987669</v>
+        <v>6987795</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3562,7 +3562,7 @@
         <v>127843631</v>
       </c>
       <c r="B31" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         <v>127843662</v>
       </c>
       <c r="B32" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>127843660</v>
       </c>
       <c r="B33" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>127843645</v>
       </c>
       <c r="B34" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3947,32 +3947,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127843666</v>
+        <v>127843630</v>
       </c>
       <c r="B35" t="n">
-        <v>79032</v>
+        <v>98571</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3982,10 +3982,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>625569</v>
+        <v>626637</v>
       </c>
       <c r="R35" t="n">
-        <v>6987664</v>
+        <v>6987919</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4012,12 +4012,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4044,32 +4044,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127843630</v>
+        <v>127843666</v>
       </c>
       <c r="B36" t="n">
-        <v>98478</v>
+        <v>79083</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4079,10 +4079,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>626637</v>
+        <v>625569</v>
       </c>
       <c r="R36" t="n">
-        <v>6987919</v>
+        <v>6987664</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4109,12 +4109,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4144,7 +4144,7 @@
         <v>127843628</v>
       </c>
       <c r="B37" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 25307-2025 artfynd.xlsx
+++ b/artfynd/A 25307-2025 artfynd.xlsx
@@ -1800,45 +1800,53 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127843625</v>
+        <v>127843622</v>
       </c>
       <c r="B13" t="n">
-        <v>98571</v>
+        <v>56876</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Valasjön Södra, Forsed, Ång</t>
+          <t>Valasjö Södra, Forsed, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626786</v>
+        <v>626173</v>
       </c>
       <c r="R13" t="n">
-        <v>6987870</v>
+        <v>6987818</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1865,12 +1873,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Hona.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1897,45 +1910,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127843649</v>
+        <v>127843625</v>
       </c>
       <c r="B14" t="n">
-        <v>79083</v>
+        <v>98571</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Valasjö Södra, Forsed, Ång</t>
+          <t>Valasjön Södra, Forsed, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626636</v>
+        <v>626786</v>
       </c>
       <c r="R14" t="n">
-        <v>6988002</v>
+        <v>6987870</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1994,7 +2007,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127843656</v>
+        <v>127843649</v>
       </c>
       <c r="B15" t="n">
         <v>79083</v>
@@ -2029,10 +2042,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626599</v>
+        <v>626636</v>
       </c>
       <c r="R15" t="n">
-        <v>6987942</v>
+        <v>6988002</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2091,53 +2104,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127843622</v>
+        <v>127843656</v>
       </c>
       <c r="B16" t="n">
-        <v>56876</v>
+        <v>79083</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Valasjö Södra, Forsed, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626173</v>
+        <v>626599</v>
       </c>
       <c r="R16" t="n">
-        <v>6987818</v>
+        <v>6987942</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2164,17 +2169,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Hona.</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2201,32 +2201,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127843633</v>
+        <v>127843651</v>
       </c>
       <c r="B17" t="n">
-        <v>98571</v>
+        <v>79083</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2236,10 +2236,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>625708</v>
+        <v>626634</v>
       </c>
       <c r="R17" t="n">
-        <v>6987784</v>
+        <v>6987851</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2266,12 +2266,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2298,32 +2298,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127843651</v>
+        <v>127843633</v>
       </c>
       <c r="B18" t="n">
-        <v>79083</v>
+        <v>98571</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2333,10 +2333,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626634</v>
+        <v>625708</v>
       </c>
       <c r="R18" t="n">
-        <v>6987851</v>
+        <v>6987784</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2363,12 +2363,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3947,32 +3947,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127843630</v>
+        <v>127843666</v>
       </c>
       <c r="B35" t="n">
-        <v>98571</v>
+        <v>79083</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3982,10 +3982,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>626637</v>
+        <v>625569</v>
       </c>
       <c r="R35" t="n">
-        <v>6987919</v>
+        <v>6987664</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4012,12 +4012,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4044,32 +4044,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127843666</v>
+        <v>127843630</v>
       </c>
       <c r="B36" t="n">
-        <v>79083</v>
+        <v>98571</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4079,10 +4079,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>625569</v>
+        <v>626637</v>
       </c>
       <c r="R36" t="n">
-        <v>6987664</v>
+        <v>6987919</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4109,12 +4109,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 25307-2025 artfynd.xlsx
+++ b/artfynd/A 25307-2025 artfynd.xlsx
@@ -913,7 +913,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127843638</v>
+        <v>127843624</v>
       </c>
       <c r="B4" t="n">
         <v>98571</v>
@@ -941,17 +941,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Valasjö Södra, Forsed, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>625697</v>
+        <v>626591</v>
       </c>
       <c r="R4" t="n">
-        <v>6987735</v>
+        <v>6987878</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,12 +982,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -992,6 +996,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1010,7 +1015,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127843624</v>
+        <v>127843638</v>
       </c>
       <c r="B5" t="n">
         <v>98571</v>
@@ -1038,21 +1043,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Valasjö Södra, Forsed, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626591</v>
+        <v>625697</v>
       </c>
       <c r="R5" t="n">
-        <v>6987878</v>
+        <v>6987735</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,12 +1080,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,7 +1094,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1112,7 +1112,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127843629</v>
+        <v>127843626</v>
       </c>
       <c r="B6" t="n">
         <v>98571</v>
@@ -1147,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626614</v>
+        <v>626538</v>
       </c>
       <c r="R6" t="n">
-        <v>6987921</v>
+        <v>6987872</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1306,7 +1306,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127843626</v>
+        <v>127843629</v>
       </c>
       <c r="B8" t="n">
         <v>98571</v>
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626538</v>
+        <v>626614</v>
       </c>
       <c r="R8" t="n">
-        <v>6987872</v>
+        <v>6987921</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -2201,32 +2201,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127843651</v>
+        <v>127843633</v>
       </c>
       <c r="B17" t="n">
-        <v>79083</v>
+        <v>98571</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2236,10 +2236,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626634</v>
+        <v>625708</v>
       </c>
       <c r="R17" t="n">
-        <v>6987851</v>
+        <v>6987784</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2266,12 +2266,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2298,32 +2298,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127843633</v>
+        <v>127843651</v>
       </c>
       <c r="B18" t="n">
-        <v>98571</v>
+        <v>79083</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2333,10 +2333,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>625708</v>
+        <v>626634</v>
       </c>
       <c r="R18" t="n">
-        <v>6987784</v>
+        <v>6987851</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2363,12 +2363,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3268,32 +3268,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127843640</v>
+        <v>127843623</v>
       </c>
       <c r="B28" t="n">
-        <v>98571</v>
+        <v>97448</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3303,10 +3303,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>625714</v>
+        <v>625778</v>
       </c>
       <c r="R28" t="n">
-        <v>6987737</v>
+        <v>6987795</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3365,7 +3365,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127843636</v>
+        <v>127843640</v>
       </c>
       <c r="B29" t="n">
         <v>98571</v>
@@ -3400,10 +3400,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>625562</v>
+        <v>625714</v>
       </c>
       <c r="R29" t="n">
-        <v>6987669</v>
+        <v>6987737</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3462,32 +3462,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127843623</v>
+        <v>127843636</v>
       </c>
       <c r="B30" t="n">
-        <v>97448</v>
+        <v>98571</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3497,10 +3497,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>625778</v>
+        <v>625562</v>
       </c>
       <c r="R30" t="n">
-        <v>6987795</v>
+        <v>6987669</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3947,32 +3947,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127843666</v>
+        <v>127843630</v>
       </c>
       <c r="B35" t="n">
-        <v>79083</v>
+        <v>98571</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3982,10 +3982,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>625569</v>
+        <v>626637</v>
       </c>
       <c r="R35" t="n">
-        <v>6987664</v>
+        <v>6987919</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4012,12 +4012,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4044,32 +4044,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127843630</v>
+        <v>127843666</v>
       </c>
       <c r="B36" t="n">
-        <v>98571</v>
+        <v>79083</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4079,10 +4079,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>626637</v>
+        <v>625569</v>
       </c>
       <c r="R36" t="n">
-        <v>6987919</v>
+        <v>6987664</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4109,12 +4109,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD36" t="b">

--- a/artfynd/A 25307-2025 artfynd.xlsx
+++ b/artfynd/A 25307-2025 artfynd.xlsx
@@ -3268,32 +3268,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127843623</v>
+        <v>127843640</v>
       </c>
       <c r="B28" t="n">
-        <v>97448</v>
+        <v>98571</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3303,10 +3303,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>625778</v>
+        <v>625714</v>
       </c>
       <c r="R28" t="n">
-        <v>6987795</v>
+        <v>6987737</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3365,7 +3365,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127843640</v>
+        <v>127843636</v>
       </c>
       <c r="B29" t="n">
         <v>98571</v>
@@ -3400,10 +3400,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>625714</v>
+        <v>625562</v>
       </c>
       <c r="R29" t="n">
-        <v>6987737</v>
+        <v>6987669</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3462,32 +3462,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127843636</v>
+        <v>127843623</v>
       </c>
       <c r="B30" t="n">
-        <v>98571</v>
+        <v>97448</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3497,10 +3497,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>625562</v>
+        <v>625778</v>
       </c>
       <c r="R30" t="n">
-        <v>6987669</v>
+        <v>6987795</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 25307-2025 artfynd.xlsx
+++ b/artfynd/A 25307-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AY53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4236,6 +4236,1554 @@
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128900396</v>
+      </c>
+      <c r="B38" t="n">
+        <v>91800</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>658</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Valasjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>626327</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6987951</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>128900379</v>
+      </c>
+      <c r="B39" t="n">
+        <v>95858</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Valasjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>626178</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6987902</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>128900406</v>
+      </c>
+      <c r="B40" t="n">
+        <v>80225</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Valasjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>626294</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6987721</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>128900389</v>
+      </c>
+      <c r="B41" t="n">
+        <v>91504</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Valasjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>626180</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6987905</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>128900398</v>
+      </c>
+      <c r="B42" t="n">
+        <v>91518</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Valasjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>626317</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6987956</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>128900384</v>
+      </c>
+      <c r="B43" t="n">
+        <v>92174</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>898</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Blackticka</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Steccherinum collabens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Fr.) Vesterholt</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Valasjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>626176</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6987909</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>128900400</v>
+      </c>
+      <c r="B44" t="n">
+        <v>91504</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Valasjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>626273</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6987791</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>128900402</v>
+      </c>
+      <c r="B45" t="n">
+        <v>80225</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Valasjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>626298</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6987747</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>128900386</v>
+      </c>
+      <c r="B46" t="n">
+        <v>91800</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>658</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Valasjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>626180</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6987905</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>128900376</v>
+      </c>
+      <c r="B47" t="n">
+        <v>91800</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>658</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Valasjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>626122</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6987885</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>128900393</v>
+      </c>
+      <c r="B48" t="n">
+        <v>91800</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>658</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Valasjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>626302</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6987979</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>128900404</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79120</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Valasjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>626312</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6987730</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>128900410</v>
+      </c>
+      <c r="B50" t="n">
+        <v>91504</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Valasjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>626191</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6987805</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>128900408</v>
+      </c>
+      <c r="B51" t="n">
+        <v>91522</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Valasjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>626287</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6987723</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>128900394</v>
+      </c>
+      <c r="B52" t="n">
+        <v>91911</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Valasjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>626302</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6987979</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>128900391</v>
+      </c>
+      <c r="B53" t="n">
+        <v>91504</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Valasjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>626302</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6987979</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Ytterlännäs</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25307-2025 artfynd.xlsx
+++ b/artfynd/A 25307-2025 artfynd.xlsx
@@ -4432,10 +4432,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128900406</v>
+        <v>128900389</v>
       </c>
       <c r="B40" t="n">
-        <v>80225</v>
+        <v>91504</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4443,21 +4443,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4467,10 +4467,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>626294</v>
+        <v>626180</v>
       </c>
       <c r="R40" t="n">
-        <v>6987721</v>
+        <v>6987905</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4529,10 +4529,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128900389</v>
+        <v>128900406</v>
       </c>
       <c r="B41" t="n">
-        <v>91504</v>
+        <v>80225</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4540,21 +4540,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4564,10 +4564,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>626180</v>
+        <v>626294</v>
       </c>
       <c r="R41" t="n">
-        <v>6987905</v>
+        <v>6987721</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5014,7 +5014,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128900386</v>
+        <v>128900376</v>
       </c>
       <c r="B46" t="n">
         <v>91800</v>
@@ -5049,10 +5049,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>626180</v>
+        <v>626122</v>
       </c>
       <c r="R46" t="n">
-        <v>6987905</v>
+        <v>6987885</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5111,7 +5111,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128900376</v>
+        <v>128900393</v>
       </c>
       <c r="B47" t="n">
         <v>91800</v>
@@ -5146,10 +5146,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>626122</v>
+        <v>626302</v>
       </c>
       <c r="R47" t="n">
-        <v>6987885</v>
+        <v>6987979</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5208,7 +5208,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128900393</v>
+        <v>128900386</v>
       </c>
       <c r="B48" t="n">
         <v>91800</v>
@@ -5243,10 +5243,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>626302</v>
+        <v>626180</v>
       </c>
       <c r="R48" t="n">
-        <v>6987979</v>
+        <v>6987905</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5596,10 +5596,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128900394</v>
+        <v>128900391</v>
       </c>
       <c r="B52" t="n">
-        <v>91911</v>
+        <v>91504</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5607,16 +5607,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5670,7 +5675,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5689,10 +5693,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128900391</v>
+        <v>128900394</v>
       </c>
       <c r="B53" t="n">
-        <v>91504</v>
+        <v>91911</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5700,21 +5704,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5768,6 +5767,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 25307-2025 artfynd.xlsx
+++ b/artfynd/A 25307-2025 artfynd.xlsx
@@ -4238,32 +4238,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128900396</v>
+        <v>128900379</v>
       </c>
       <c r="B38" t="n">
-        <v>91800</v>
+        <v>95858</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>2809</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4273,10 +4273,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>626327</v>
+        <v>626178</v>
       </c>
       <c r="R38" t="n">
-        <v>6987951</v>
+        <v>6987902</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4335,32 +4335,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128900379</v>
+        <v>128900396</v>
       </c>
       <c r="B39" t="n">
-        <v>95858</v>
+        <v>91800</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2809</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4370,10 +4370,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>626178</v>
+        <v>626327</v>
       </c>
       <c r="R39" t="n">
-        <v>6987902</v>
+        <v>6987951</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5014,7 +5014,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128900376</v>
+        <v>128900386</v>
       </c>
       <c r="B46" t="n">
         <v>91800</v>
@@ -5049,10 +5049,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>626122</v>
+        <v>626180</v>
       </c>
       <c r="R46" t="n">
-        <v>6987885</v>
+        <v>6987905</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5111,7 +5111,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128900393</v>
+        <v>128900376</v>
       </c>
       <c r="B47" t="n">
         <v>91800</v>
@@ -5146,10 +5146,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>626302</v>
+        <v>626122</v>
       </c>
       <c r="R47" t="n">
-        <v>6987979</v>
+        <v>6987885</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5208,7 +5208,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128900386</v>
+        <v>128900393</v>
       </c>
       <c r="B48" t="n">
         <v>91800</v>
@@ -5243,10 +5243,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>626180</v>
+        <v>626302</v>
       </c>
       <c r="R48" t="n">
-        <v>6987905</v>
+        <v>6987979</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>

--- a/artfynd/A 25307-2025 artfynd.xlsx
+++ b/artfynd/A 25307-2025 artfynd.xlsx
@@ -4238,32 +4238,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128900379</v>
+        <v>128900396</v>
       </c>
       <c r="B38" t="n">
-        <v>95858</v>
+        <v>91804</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2809</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4273,10 +4273,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>626178</v>
+        <v>626327</v>
       </c>
       <c r="R38" t="n">
-        <v>6987902</v>
+        <v>6987951</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4335,32 +4335,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128900396</v>
+        <v>128900379</v>
       </c>
       <c r="B39" t="n">
-        <v>91800</v>
+        <v>95862</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>2809</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4370,10 +4370,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>626327</v>
+        <v>626178</v>
       </c>
       <c r="R39" t="n">
-        <v>6987951</v>
+        <v>6987902</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4435,7 +4435,7 @@
         <v>128900389</v>
       </c>
       <c r="B40" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>128900406</v>
       </c>
       <c r="B41" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
         <v>128900398</v>
       </c>
       <c r="B42" t="n">
-        <v>91518</v>
+        <v>91522</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4723,32 +4723,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128900384</v>
+        <v>128900400</v>
       </c>
       <c r="B43" t="n">
-        <v>92174</v>
+        <v>91508</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4758,10 +4758,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>626176</v>
+        <v>626273</v>
       </c>
       <c r="R43" t="n">
-        <v>6987909</v>
+        <v>6987791</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4820,32 +4820,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128900400</v>
+        <v>128900384</v>
       </c>
       <c r="B44" t="n">
-        <v>91504</v>
+        <v>92178</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>898</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4855,10 +4855,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>626273</v>
+        <v>626176</v>
       </c>
       <c r="R44" t="n">
-        <v>6987791</v>
+        <v>6987909</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4920,7 +4920,7 @@
         <v>128900402</v>
       </c>
       <c r="B45" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>128900386</v>
       </c>
       <c r="B46" t="n">
-        <v>91800</v>
+        <v>91804</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>128900376</v>
       </c>
       <c r="B47" t="n">
-        <v>91800</v>
+        <v>91804</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5211,7 +5211,7 @@
         <v>128900393</v>
       </c>
       <c r="B48" t="n">
-        <v>91800</v>
+        <v>91804</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
         <v>128900404</v>
       </c>
       <c r="B49" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>128900410</v>
       </c>
       <c r="B50" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>128900408</v>
       </c>
       <c r="B51" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5596,10 +5596,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128900391</v>
+        <v>128900394</v>
       </c>
       <c r="B52" t="n">
-        <v>91504</v>
+        <v>91915</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5607,21 +5607,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5675,6 +5670,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5693,10 +5689,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128900394</v>
+        <v>128900391</v>
       </c>
       <c r="B53" t="n">
-        <v>91911</v>
+        <v>91508</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5704,16 +5700,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5767,7 +5768,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 25307-2025 artfynd.xlsx
+++ b/artfynd/A 25307-2025 artfynd.xlsx
@@ -4238,32 +4238,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128900396</v>
+        <v>128900379</v>
       </c>
       <c r="B38" t="n">
-        <v>91804</v>
+        <v>95862</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>2809</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4273,10 +4273,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>626327</v>
+        <v>626178</v>
       </c>
       <c r="R38" t="n">
-        <v>6987951</v>
+        <v>6987902</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4335,32 +4335,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128900379</v>
+        <v>128900396</v>
       </c>
       <c r="B39" t="n">
-        <v>95862</v>
+        <v>91804</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2809</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4370,10 +4370,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>626178</v>
+        <v>626327</v>
       </c>
       <c r="R39" t="n">
-        <v>6987902</v>
+        <v>6987951</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4432,10 +4432,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128900389</v>
+        <v>128900406</v>
       </c>
       <c r="B40" t="n">
-        <v>91508</v>
+        <v>80229</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4443,21 +4443,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4467,10 +4467,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>626180</v>
+        <v>626294</v>
       </c>
       <c r="R40" t="n">
-        <v>6987905</v>
+        <v>6987721</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4529,10 +4529,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128900406</v>
+        <v>128900389</v>
       </c>
       <c r="B41" t="n">
-        <v>80229</v>
+        <v>91508</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4540,21 +4540,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4564,10 +4564,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>626294</v>
+        <v>626180</v>
       </c>
       <c r="R41" t="n">
-        <v>6987721</v>
+        <v>6987905</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4723,32 +4723,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128900400</v>
+        <v>128900384</v>
       </c>
       <c r="B43" t="n">
-        <v>91508</v>
+        <v>92178</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>898</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4758,10 +4758,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>626273</v>
+        <v>626176</v>
       </c>
       <c r="R43" t="n">
-        <v>6987791</v>
+        <v>6987909</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4820,32 +4820,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128900384</v>
+        <v>128900400</v>
       </c>
       <c r="B44" t="n">
-        <v>92178</v>
+        <v>91508</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4855,10 +4855,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>626176</v>
+        <v>626273</v>
       </c>
       <c r="R44" t="n">
-        <v>6987909</v>
+        <v>6987791</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5402,10 +5402,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128900410</v>
+        <v>128900408</v>
       </c>
       <c r="B50" t="n">
-        <v>91508</v>
+        <v>91526</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5413,21 +5413,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5437,10 +5437,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>626191</v>
+        <v>626287</v>
       </c>
       <c r="R50" t="n">
-        <v>6987805</v>
+        <v>6987723</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5499,10 +5499,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128900408</v>
+        <v>128900410</v>
       </c>
       <c r="B51" t="n">
-        <v>91526</v>
+        <v>91508</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5510,21 +5510,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5534,10 +5534,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>626287</v>
+        <v>626191</v>
       </c>
       <c r="R51" t="n">
-        <v>6987723</v>
+        <v>6987805</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5596,10 +5596,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128900394</v>
+        <v>128900391</v>
       </c>
       <c r="B52" t="n">
-        <v>91915</v>
+        <v>91508</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5607,16 +5607,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5670,7 +5675,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5689,10 +5693,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128900391</v>
+        <v>128900394</v>
       </c>
       <c r="B53" t="n">
-        <v>91508</v>
+        <v>91915</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5700,21 +5704,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5768,6 +5767,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 25307-2025 artfynd.xlsx
+++ b/artfynd/A 25307-2025 artfynd.xlsx
@@ -4238,32 +4238,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128900379</v>
+        <v>128900396</v>
       </c>
       <c r="B38" t="n">
-        <v>95862</v>
+        <v>91804</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2809</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4273,10 +4273,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>626178</v>
+        <v>626327</v>
       </c>
       <c r="R38" t="n">
-        <v>6987902</v>
+        <v>6987951</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4335,32 +4335,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128900396</v>
+        <v>128900379</v>
       </c>
       <c r="B39" t="n">
-        <v>91804</v>
+        <v>95862</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>2809</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4370,10 +4370,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>626327</v>
+        <v>626178</v>
       </c>
       <c r="R39" t="n">
-        <v>6987951</v>
+        <v>6987902</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4432,10 +4432,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128900406</v>
+        <v>128900389</v>
       </c>
       <c r="B40" t="n">
-        <v>80229</v>
+        <v>91508</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4443,21 +4443,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4467,10 +4467,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>626294</v>
+        <v>626180</v>
       </c>
       <c r="R40" t="n">
-        <v>6987721</v>
+        <v>6987905</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4529,10 +4529,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128900389</v>
+        <v>128900406</v>
       </c>
       <c r="B41" t="n">
-        <v>91508</v>
+        <v>80229</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4540,21 +4540,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4564,10 +4564,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>626180</v>
+        <v>626294</v>
       </c>
       <c r="R41" t="n">
-        <v>6987905</v>
+        <v>6987721</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5402,10 +5402,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128900408</v>
+        <v>128900410</v>
       </c>
       <c r="B50" t="n">
-        <v>91526</v>
+        <v>91508</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5413,21 +5413,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5437,10 +5437,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>626287</v>
+        <v>626191</v>
       </c>
       <c r="R50" t="n">
-        <v>6987723</v>
+        <v>6987805</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5499,10 +5499,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128900410</v>
+        <v>128900408</v>
       </c>
       <c r="B51" t="n">
-        <v>91508</v>
+        <v>91526</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5510,21 +5510,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5534,10 +5534,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>626191</v>
+        <v>626287</v>
       </c>
       <c r="R51" t="n">
-        <v>6987805</v>
+        <v>6987723</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>

--- a/artfynd/A 25307-2025 artfynd.xlsx
+++ b/artfynd/A 25307-2025 artfynd.xlsx
@@ -4241,7 +4241,7 @@
         <v>128900396</v>
       </c>
       <c r="B38" t="n">
-        <v>91804</v>
+        <v>91809</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4338,7 +4338,7 @@
         <v>128900379</v>
       </c>
       <c r="B39" t="n">
-        <v>95862</v>
+        <v>95869</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         <v>128900389</v>
       </c>
       <c r="B40" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>128900406</v>
       </c>
       <c r="B41" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
         <v>128900398</v>
       </c>
       <c r="B42" t="n">
-        <v>91522</v>
+        <v>91527</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
         <v>128900384</v>
       </c>
       <c r="B43" t="n">
-        <v>92178</v>
+        <v>92183</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
         <v>128900400</v>
       </c>
       <c r="B44" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4920,7 +4920,7 @@
         <v>128900402</v>
       </c>
       <c r="B45" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>128900386</v>
       </c>
       <c r="B46" t="n">
-        <v>91804</v>
+        <v>91809</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>128900376</v>
       </c>
       <c r="B47" t="n">
-        <v>91804</v>
+        <v>91809</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5211,7 +5211,7 @@
         <v>128900393</v>
       </c>
       <c r="B48" t="n">
-        <v>91804</v>
+        <v>91809</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
         <v>128900404</v>
       </c>
       <c r="B49" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>128900410</v>
       </c>
       <c r="B50" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>128900408</v>
       </c>
       <c r="B51" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5599,7 +5599,7 @@
         <v>128900391</v>
       </c>
       <c r="B52" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>128900394</v>
       </c>
       <c r="B53" t="n">
-        <v>91915</v>
+        <v>91920</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 25307-2025 artfynd.xlsx
+++ b/artfynd/A 25307-2025 artfynd.xlsx
@@ -4238,32 +4238,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128900396</v>
+        <v>128900379</v>
       </c>
       <c r="B38" t="n">
-        <v>91805</v>
+        <v>95877</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>2809</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4273,10 +4273,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>626327</v>
+        <v>626178</v>
       </c>
       <c r="R38" t="n">
-        <v>6987951</v>
+        <v>6987902</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4335,32 +4335,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128900379</v>
+        <v>128900396</v>
       </c>
       <c r="B39" t="n">
-        <v>95877</v>
+        <v>91805</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2809</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4370,10 +4370,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>626178</v>
+        <v>626327</v>
       </c>
       <c r="R39" t="n">
-        <v>6987902</v>
+        <v>6987951</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>

--- a/artfynd/A 25307-2025 artfynd.xlsx
+++ b/artfynd/A 25307-2025 artfynd.xlsx
@@ -4238,32 +4238,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128900379</v>
+        <v>128900396</v>
       </c>
       <c r="B38" t="n">
-        <v>95877</v>
+        <v>91808</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2809</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4273,10 +4273,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>626178</v>
+        <v>626327</v>
       </c>
       <c r="R38" t="n">
-        <v>6987902</v>
+        <v>6987951</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4335,32 +4335,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128900396</v>
+        <v>128900379</v>
       </c>
       <c r="B39" t="n">
-        <v>91805</v>
+        <v>95882</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>2809</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4370,10 +4370,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>626327</v>
+        <v>626178</v>
       </c>
       <c r="R39" t="n">
-        <v>6987951</v>
+        <v>6987902</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4432,10 +4432,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128900389</v>
+        <v>128900406</v>
       </c>
       <c r="B40" t="n">
-        <v>91520</v>
+        <v>80139</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4443,21 +4443,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4467,10 +4467,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>626180</v>
+        <v>626294</v>
       </c>
       <c r="R40" t="n">
-        <v>6987905</v>
+        <v>6987721</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4529,10 +4529,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128900406</v>
+        <v>128900389</v>
       </c>
       <c r="B41" t="n">
-        <v>80139</v>
+        <v>91523</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4540,21 +4540,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4564,10 +4564,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>626294</v>
+        <v>626180</v>
       </c>
       <c r="R41" t="n">
-        <v>6987721</v>
+        <v>6987905</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4629,7 +4629,7 @@
         <v>128900398</v>
       </c>
       <c r="B42" t="n">
-        <v>91534</v>
+        <v>91537</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
         <v>128900384</v>
       </c>
       <c r="B43" t="n">
-        <v>92191</v>
+        <v>92196</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
         <v>128900400</v>
       </c>
       <c r="B44" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>128900386</v>
       </c>
       <c r="B46" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>128900376</v>
       </c>
       <c r="B47" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5211,7 +5211,7 @@
         <v>128900393</v>
       </c>
       <c r="B48" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5402,10 +5402,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128900410</v>
+        <v>128900408</v>
       </c>
       <c r="B50" t="n">
-        <v>91520</v>
+        <v>91541</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5413,21 +5413,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5437,10 +5437,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>626191</v>
+        <v>626287</v>
       </c>
       <c r="R50" t="n">
-        <v>6987805</v>
+        <v>6987723</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5499,10 +5499,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128900408</v>
+        <v>128900410</v>
       </c>
       <c r="B51" t="n">
-        <v>91538</v>
+        <v>91523</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5510,21 +5510,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5534,10 +5534,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>626287</v>
+        <v>626191</v>
       </c>
       <c r="R51" t="n">
-        <v>6987723</v>
+        <v>6987805</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5596,10 +5596,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128900391</v>
+        <v>128900394</v>
       </c>
       <c r="B52" t="n">
-        <v>91520</v>
+        <v>91931</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5607,21 +5607,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5675,6 +5670,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5693,10 +5689,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128900394</v>
+        <v>128900391</v>
       </c>
       <c r="B53" t="n">
-        <v>91928</v>
+        <v>91523</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5704,16 +5700,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5767,7 +5768,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 25307-2025 artfynd.xlsx
+++ b/artfynd/A 25307-2025 artfynd.xlsx
@@ -4238,32 +4238,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128900396</v>
+        <v>128900379</v>
       </c>
       <c r="B38" t="n">
-        <v>91808</v>
+        <v>95885</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>2809</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4273,10 +4273,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>626327</v>
+        <v>626178</v>
       </c>
       <c r="R38" t="n">
-        <v>6987951</v>
+        <v>6987902</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4335,32 +4335,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128900379</v>
+        <v>128900396</v>
       </c>
       <c r="B39" t="n">
-        <v>95882</v>
+        <v>91811</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2809</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4370,10 +4370,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>626178</v>
+        <v>626327</v>
       </c>
       <c r="R39" t="n">
-        <v>6987902</v>
+        <v>6987951</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4432,10 +4432,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128900406</v>
+        <v>128900389</v>
       </c>
       <c r="B40" t="n">
-        <v>80139</v>
+        <v>91526</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4443,21 +4443,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4467,10 +4467,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>626294</v>
+        <v>626180</v>
       </c>
       <c r="R40" t="n">
-        <v>6987721</v>
+        <v>6987905</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4529,10 +4529,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128900389</v>
+        <v>128900406</v>
       </c>
       <c r="B41" t="n">
-        <v>91523</v>
+        <v>80140</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4540,21 +4540,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4564,10 +4564,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>626180</v>
+        <v>626294</v>
       </c>
       <c r="R41" t="n">
-        <v>6987905</v>
+        <v>6987721</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4626,32 +4626,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128900398</v>
+        <v>128900384</v>
       </c>
       <c r="B42" t="n">
-        <v>91537</v>
+        <v>92199</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1204</v>
+        <v>898</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4661,10 +4661,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>626317</v>
+        <v>626176</v>
       </c>
       <c r="R42" t="n">
-        <v>6987956</v>
+        <v>6987909</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4723,32 +4723,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128900384</v>
+        <v>128900398</v>
       </c>
       <c r="B43" t="n">
-        <v>92196</v>
+        <v>91540</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>898</v>
+        <v>1204</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4758,10 +4758,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>626176</v>
+        <v>626317</v>
       </c>
       <c r="R43" t="n">
-        <v>6987909</v>
+        <v>6987956</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4823,7 +4823,7 @@
         <v>128900400</v>
       </c>
       <c r="B44" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4920,7 +4920,7 @@
         <v>128900402</v>
       </c>
       <c r="B45" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>128900386</v>
       </c>
       <c r="B46" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>128900376</v>
       </c>
       <c r="B47" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5211,7 +5211,7 @@
         <v>128900393</v>
       </c>
       <c r="B48" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
         <v>128900404</v>
       </c>
       <c r="B49" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5402,10 +5402,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128900408</v>
+        <v>128900410</v>
       </c>
       <c r="B50" t="n">
-        <v>91541</v>
+        <v>91526</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5413,21 +5413,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5437,10 +5437,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>626287</v>
+        <v>626191</v>
       </c>
       <c r="R50" t="n">
-        <v>6987723</v>
+        <v>6987805</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5499,10 +5499,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128900410</v>
+        <v>128900408</v>
       </c>
       <c r="B51" t="n">
-        <v>91523</v>
+        <v>91544</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5510,21 +5510,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5534,10 +5534,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>626191</v>
+        <v>626287</v>
       </c>
       <c r="R51" t="n">
-        <v>6987805</v>
+        <v>6987723</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5596,10 +5596,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128900394</v>
+        <v>128900391</v>
       </c>
       <c r="B52" t="n">
-        <v>91931</v>
+        <v>91526</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5607,16 +5607,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5670,7 +5675,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5689,10 +5693,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128900391</v>
+        <v>128900394</v>
       </c>
       <c r="B53" t="n">
-        <v>91523</v>
+        <v>91934</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5700,21 +5704,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5768,6 +5767,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 25307-2025 artfynd.xlsx
+++ b/artfynd/A 25307-2025 artfynd.xlsx
@@ -4432,10 +4432,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128900389</v>
+        <v>128900406</v>
       </c>
       <c r="B40" t="n">
-        <v>91526</v>
+        <v>80140</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4443,21 +4443,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4467,10 +4467,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>626180</v>
+        <v>626294</v>
       </c>
       <c r="R40" t="n">
-        <v>6987905</v>
+        <v>6987721</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4529,10 +4529,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128900406</v>
+        <v>128900389</v>
       </c>
       <c r="B41" t="n">
-        <v>80140</v>
+        <v>91526</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4540,21 +4540,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4564,10 +4564,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>626294</v>
+        <v>626180</v>
       </c>
       <c r="R41" t="n">
-        <v>6987721</v>
+        <v>6987905</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4626,32 +4626,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128900384</v>
+        <v>128900398</v>
       </c>
       <c r="B42" t="n">
-        <v>92199</v>
+        <v>91540</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>898</v>
+        <v>1204</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4661,10 +4661,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>626176</v>
+        <v>626317</v>
       </c>
       <c r="R42" t="n">
-        <v>6987909</v>
+        <v>6987956</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4723,32 +4723,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128900398</v>
+        <v>128900384</v>
       </c>
       <c r="B43" t="n">
-        <v>91540</v>
+        <v>92199</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1204</v>
+        <v>898</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4758,10 +4758,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>626317</v>
+        <v>626176</v>
       </c>
       <c r="R43" t="n">
-        <v>6987956</v>
+        <v>6987909</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5596,10 +5596,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128900391</v>
+        <v>128900394</v>
       </c>
       <c r="B52" t="n">
-        <v>91526</v>
+        <v>91934</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5607,21 +5607,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5675,6 +5670,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5693,10 +5689,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128900394</v>
+        <v>128900391</v>
       </c>
       <c r="B53" t="n">
-        <v>91934</v>
+        <v>91526</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5704,16 +5700,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5767,7 +5768,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 25307-2025 artfynd.xlsx
+++ b/artfynd/A 25307-2025 artfynd.xlsx
@@ -4432,10 +4432,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128900406</v>
+        <v>128900389</v>
       </c>
       <c r="B40" t="n">
-        <v>80140</v>
+        <v>91526</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4443,21 +4443,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4467,10 +4467,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>626294</v>
+        <v>626180</v>
       </c>
       <c r="R40" t="n">
-        <v>6987721</v>
+        <v>6987905</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4529,10 +4529,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128900389</v>
+        <v>128900406</v>
       </c>
       <c r="B41" t="n">
-        <v>91526</v>
+        <v>80140</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4540,21 +4540,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4564,10 +4564,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>626180</v>
+        <v>626294</v>
       </c>
       <c r="R41" t="n">
-        <v>6987905</v>
+        <v>6987721</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5014,7 +5014,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128900386</v>
+        <v>128900393</v>
       </c>
       <c r="B46" t="n">
         <v>91811</v>
@@ -5049,10 +5049,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>626180</v>
+        <v>626302</v>
       </c>
       <c r="R46" t="n">
-        <v>6987905</v>
+        <v>6987979</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5111,7 +5111,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128900376</v>
+        <v>128900386</v>
       </c>
       <c r="B47" t="n">
         <v>91811</v>
@@ -5146,10 +5146,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>626122</v>
+        <v>626180</v>
       </c>
       <c r="R47" t="n">
-        <v>6987885</v>
+        <v>6987905</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5208,7 +5208,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128900393</v>
+        <v>128900376</v>
       </c>
       <c r="B48" t="n">
         <v>91811</v>
@@ -5243,10 +5243,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>626302</v>
+        <v>626122</v>
       </c>
       <c r="R48" t="n">
-        <v>6987979</v>
+        <v>6987885</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>

--- a/artfynd/A 25307-2025 artfynd.xlsx
+++ b/artfynd/A 25307-2025 artfynd.xlsx
@@ -5014,7 +5014,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128900393</v>
+        <v>128900386</v>
       </c>
       <c r="B46" t="n">
         <v>91811</v>
@@ -5049,10 +5049,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>626302</v>
+        <v>626180</v>
       </c>
       <c r="R46" t="n">
-        <v>6987979</v>
+        <v>6987905</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5111,7 +5111,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128900386</v>
+        <v>128900376</v>
       </c>
       <c r="B47" t="n">
         <v>91811</v>
@@ -5146,10 +5146,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>626180</v>
+        <v>626122</v>
       </c>
       <c r="R47" t="n">
-        <v>6987905</v>
+        <v>6987885</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5208,7 +5208,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128900376</v>
+        <v>128900393</v>
       </c>
       <c r="B48" t="n">
         <v>91811</v>
@@ -5243,10 +5243,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>626122</v>
+        <v>626302</v>
       </c>
       <c r="R48" t="n">
-        <v>6987885</v>
+        <v>6987979</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5402,10 +5402,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128900410</v>
+        <v>128900408</v>
       </c>
       <c r="B50" t="n">
-        <v>91526</v>
+        <v>91544</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5413,21 +5413,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5437,10 +5437,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>626191</v>
+        <v>626287</v>
       </c>
       <c r="R50" t="n">
-        <v>6987805</v>
+        <v>6987723</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5499,10 +5499,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128900408</v>
+        <v>128900410</v>
       </c>
       <c r="B51" t="n">
-        <v>91544</v>
+        <v>91526</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5510,21 +5510,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5534,10 +5534,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>626287</v>
+        <v>626191</v>
       </c>
       <c r="R51" t="n">
-        <v>6987723</v>
+        <v>6987805</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5596,10 +5596,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128900394</v>
+        <v>128900391</v>
       </c>
       <c r="B52" t="n">
-        <v>91934</v>
+        <v>91526</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5607,16 +5607,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5670,7 +5675,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5689,10 +5693,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128900391</v>
+        <v>128900394</v>
       </c>
       <c r="B53" t="n">
-        <v>91526</v>
+        <v>91934</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5700,21 +5704,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5768,6 +5767,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 25307-2025 artfynd.xlsx
+++ b/artfynd/A 25307-2025 artfynd.xlsx
@@ -4241,7 +4241,7 @@
         <v>128900379</v>
       </c>
       <c r="B38" t="n">
-        <v>95885</v>
+        <v>95895</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4338,7 +4338,7 @@
         <v>128900396</v>
       </c>
       <c r="B39" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         <v>128900389</v>
       </c>
       <c r="B40" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>128900406</v>
       </c>
       <c r="B41" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
         <v>128900398</v>
       </c>
       <c r="B42" t="n">
-        <v>91540</v>
+        <v>91547</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
         <v>128900384</v>
       </c>
       <c r="B43" t="n">
-        <v>92199</v>
+        <v>92206</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
         <v>128900400</v>
       </c>
       <c r="B44" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4920,7 +4920,7 @@
         <v>128900402</v>
       </c>
       <c r="B45" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>128900386</v>
       </c>
       <c r="B46" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>128900376</v>
       </c>
       <c r="B47" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5211,7 +5211,7 @@
         <v>128900393</v>
       </c>
       <c r="B48" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
         <v>128900404</v>
       </c>
       <c r="B49" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5402,10 +5402,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128900408</v>
+        <v>128900410</v>
       </c>
       <c r="B50" t="n">
-        <v>91544</v>
+        <v>91533</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5413,21 +5413,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5437,10 +5437,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>626287</v>
+        <v>626191</v>
       </c>
       <c r="R50" t="n">
-        <v>6987723</v>
+        <v>6987805</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5499,10 +5499,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128900410</v>
+        <v>128900408</v>
       </c>
       <c r="B51" t="n">
-        <v>91526</v>
+        <v>91551</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5510,21 +5510,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5534,10 +5534,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>626191</v>
+        <v>626287</v>
       </c>
       <c r="R51" t="n">
-        <v>6987805</v>
+        <v>6987723</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5596,10 +5596,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128900391</v>
+        <v>128900394</v>
       </c>
       <c r="B52" t="n">
-        <v>91526</v>
+        <v>91941</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5607,21 +5607,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5675,6 +5670,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5693,10 +5689,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128900394</v>
+        <v>128900391</v>
       </c>
       <c r="B53" t="n">
-        <v>91934</v>
+        <v>91533</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5704,16 +5700,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5767,7 +5768,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 25307-2025 artfynd.xlsx
+++ b/artfynd/A 25307-2025 artfynd.xlsx
@@ -4238,32 +4238,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128900379</v>
+        <v>128900396</v>
       </c>
       <c r="B38" t="n">
-        <v>95895</v>
+        <v>91825</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2809</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4273,10 +4273,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>626178</v>
+        <v>626327</v>
       </c>
       <c r="R38" t="n">
-        <v>6987902</v>
+        <v>6987951</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4335,32 +4335,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128900396</v>
+        <v>128900379</v>
       </c>
       <c r="B39" t="n">
-        <v>91818</v>
+        <v>95902</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>2809</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4370,10 +4370,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>626327</v>
+        <v>626178</v>
       </c>
       <c r="R39" t="n">
-        <v>6987951</v>
+        <v>6987902</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4435,7 +4435,7 @@
         <v>128900389</v>
       </c>
       <c r="B40" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
         <v>128900398</v>
       </c>
       <c r="B42" t="n">
-        <v>91547</v>
+        <v>91554</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
         <v>128900384</v>
       </c>
       <c r="B43" t="n">
-        <v>92206</v>
+        <v>92213</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
         <v>128900400</v>
       </c>
       <c r="B44" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5014,10 +5014,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128900386</v>
+        <v>128900393</v>
       </c>
       <c r="B46" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5049,10 +5049,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>626180</v>
+        <v>626302</v>
       </c>
       <c r="R46" t="n">
-        <v>6987905</v>
+        <v>6987979</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5114,7 +5114,7 @@
         <v>128900376</v>
       </c>
       <c r="B47" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5208,10 +5208,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128900393</v>
+        <v>128900386</v>
       </c>
       <c r="B48" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5243,10 +5243,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>626302</v>
+        <v>626180</v>
       </c>
       <c r="R48" t="n">
-        <v>6987979</v>
+        <v>6987905</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5402,10 +5402,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128900410</v>
+        <v>128900408</v>
       </c>
       <c r="B50" t="n">
-        <v>91533</v>
+        <v>91558</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5413,21 +5413,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5437,10 +5437,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>626191</v>
+        <v>626287</v>
       </c>
       <c r="R50" t="n">
-        <v>6987805</v>
+        <v>6987723</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5499,10 +5499,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128900408</v>
+        <v>128900410</v>
       </c>
       <c r="B51" t="n">
-        <v>91551</v>
+        <v>91540</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5510,21 +5510,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5534,10 +5534,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>626287</v>
+        <v>626191</v>
       </c>
       <c r="R51" t="n">
-        <v>6987723</v>
+        <v>6987805</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5596,10 +5596,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128900394</v>
+        <v>128900391</v>
       </c>
       <c r="B52" t="n">
-        <v>91941</v>
+        <v>91540</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5607,16 +5607,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5670,7 +5675,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5689,10 +5693,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128900391</v>
+        <v>128900394</v>
       </c>
       <c r="B53" t="n">
-        <v>91533</v>
+        <v>91948</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5700,21 +5704,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5768,6 +5767,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 25307-2025 artfynd.xlsx
+++ b/artfynd/A 25307-2025 artfynd.xlsx
@@ -4238,32 +4238,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128900396</v>
+        <v>128900379</v>
       </c>
       <c r="B38" t="n">
-        <v>91825</v>
+        <v>95904</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>2809</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4273,10 +4273,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>626327</v>
+        <v>626178</v>
       </c>
       <c r="R38" t="n">
-        <v>6987951</v>
+        <v>6987902</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4335,32 +4335,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128900379</v>
+        <v>128900396</v>
       </c>
       <c r="B39" t="n">
-        <v>95902</v>
+        <v>91827</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2809</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4370,10 +4370,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>626178</v>
+        <v>626327</v>
       </c>
       <c r="R39" t="n">
-        <v>6987902</v>
+        <v>6987951</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4432,10 +4432,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128900389</v>
+        <v>128900406</v>
       </c>
       <c r="B40" t="n">
-        <v>91540</v>
+        <v>80146</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4443,21 +4443,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4467,10 +4467,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>626180</v>
+        <v>626294</v>
       </c>
       <c r="R40" t="n">
-        <v>6987905</v>
+        <v>6987721</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4529,10 +4529,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128900406</v>
+        <v>128900389</v>
       </c>
       <c r="B41" t="n">
-        <v>80144</v>
+        <v>91542</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4540,21 +4540,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4564,10 +4564,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>626294</v>
+        <v>626180</v>
       </c>
       <c r="R41" t="n">
-        <v>6987721</v>
+        <v>6987905</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4629,7 +4629,7 @@
         <v>128900398</v>
       </c>
       <c r="B42" t="n">
-        <v>91554</v>
+        <v>91556</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
         <v>128900384</v>
       </c>
       <c r="B43" t="n">
-        <v>92213</v>
+        <v>92215</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
         <v>128900400</v>
       </c>
       <c r="B44" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4920,7 +4920,7 @@
         <v>128900402</v>
       </c>
       <c r="B45" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5014,10 +5014,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128900393</v>
+        <v>128900386</v>
       </c>
       <c r="B46" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5049,10 +5049,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>626302</v>
+        <v>626180</v>
       </c>
       <c r="R46" t="n">
-        <v>6987979</v>
+        <v>6987905</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5114,7 +5114,7 @@
         <v>128900376</v>
       </c>
       <c r="B47" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5208,10 +5208,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128900386</v>
+        <v>128900393</v>
       </c>
       <c r="B48" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5243,10 +5243,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>626180</v>
+        <v>626302</v>
       </c>
       <c r="R48" t="n">
-        <v>6987905</v>
+        <v>6987979</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5308,7 +5308,7 @@
         <v>128900404</v>
       </c>
       <c r="B49" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>128900408</v>
       </c>
       <c r="B50" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>128900410</v>
       </c>
       <c r="B51" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5596,10 +5596,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128900391</v>
+        <v>128900394</v>
       </c>
       <c r="B52" t="n">
-        <v>91540</v>
+        <v>91950</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5607,21 +5607,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5675,6 +5670,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5693,10 +5689,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128900394</v>
+        <v>128900391</v>
       </c>
       <c r="B53" t="n">
-        <v>91948</v>
+        <v>91542</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5704,16 +5700,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5767,7 +5768,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 25307-2025 artfynd.xlsx
+++ b/artfynd/A 25307-2025 artfynd.xlsx
@@ -4432,10 +4432,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128900406</v>
+        <v>128900389</v>
       </c>
       <c r="B40" t="n">
-        <v>80146</v>
+        <v>91542</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4443,21 +4443,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4467,10 +4467,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>626294</v>
+        <v>626180</v>
       </c>
       <c r="R40" t="n">
-        <v>6987721</v>
+        <v>6987905</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4529,10 +4529,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128900389</v>
+        <v>128900406</v>
       </c>
       <c r="B41" t="n">
-        <v>91542</v>
+        <v>80146</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4540,21 +4540,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4564,10 +4564,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>626180</v>
+        <v>626294</v>
       </c>
       <c r="R41" t="n">
-        <v>6987905</v>
+        <v>6987721</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5402,10 +5402,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128900408</v>
+        <v>128900410</v>
       </c>
       <c r="B50" t="n">
-        <v>91560</v>
+        <v>91542</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5413,21 +5413,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5437,10 +5437,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>626287</v>
+        <v>626191</v>
       </c>
       <c r="R50" t="n">
-        <v>6987723</v>
+        <v>6987805</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5499,10 +5499,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128900410</v>
+        <v>128900408</v>
       </c>
       <c r="B51" t="n">
-        <v>91542</v>
+        <v>91560</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5510,21 +5510,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5534,10 +5534,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>626191</v>
+        <v>626287</v>
       </c>
       <c r="R51" t="n">
-        <v>6987805</v>
+        <v>6987723</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5596,10 +5596,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128900394</v>
+        <v>128900391</v>
       </c>
       <c r="B52" t="n">
-        <v>91950</v>
+        <v>91542</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5607,16 +5607,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5670,7 +5675,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5689,10 +5693,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128900391</v>
+        <v>128900394</v>
       </c>
       <c r="B53" t="n">
-        <v>91542</v>
+        <v>91950</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5700,21 +5704,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5768,6 +5767,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 25307-2025 artfynd.xlsx
+++ b/artfynd/A 25307-2025 artfynd.xlsx
@@ -5596,10 +5596,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128900391</v>
+        <v>128900394</v>
       </c>
       <c r="B52" t="n">
-        <v>91542</v>
+        <v>91950</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5607,21 +5607,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5675,6 +5670,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5693,10 +5689,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128900394</v>
+        <v>128900391</v>
       </c>
       <c r="B53" t="n">
-        <v>91950</v>
+        <v>91542</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5704,16 +5700,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5767,7 +5768,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 25307-2025 artfynd.xlsx
+++ b/artfynd/A 25307-2025 artfynd.xlsx
@@ -4238,32 +4238,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128900379</v>
+        <v>128900396</v>
       </c>
       <c r="B38" t="n">
-        <v>95904</v>
+        <v>91837</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2809</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4273,10 +4273,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>626178</v>
+        <v>626327</v>
       </c>
       <c r="R38" t="n">
-        <v>6987902</v>
+        <v>6987951</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4335,32 +4335,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128900396</v>
+        <v>128900379</v>
       </c>
       <c r="B39" t="n">
-        <v>91827</v>
+        <v>95930</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>2809</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4370,10 +4370,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>626327</v>
+        <v>626178</v>
       </c>
       <c r="R39" t="n">
-        <v>6987951</v>
+        <v>6987902</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4435,7 +4435,7 @@
         <v>128900389</v>
       </c>
       <c r="B40" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
         <v>128900398</v>
       </c>
       <c r="B42" t="n">
-        <v>91556</v>
+        <v>91554</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
         <v>128900384</v>
       </c>
       <c r="B43" t="n">
-        <v>92215</v>
+        <v>92230</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
         <v>128900400</v>
       </c>
       <c r="B44" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>128900386</v>
       </c>
       <c r="B46" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>128900376</v>
       </c>
       <c r="B47" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5211,7 +5211,7 @@
         <v>128900393</v>
       </c>
       <c r="B48" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5402,10 +5402,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128900410</v>
+        <v>128900408</v>
       </c>
       <c r="B50" t="n">
-        <v>91542</v>
+        <v>91558</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5413,21 +5413,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5437,10 +5437,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>626191</v>
+        <v>626287</v>
       </c>
       <c r="R50" t="n">
-        <v>6987805</v>
+        <v>6987723</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5499,10 +5499,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128900408</v>
+        <v>128900410</v>
       </c>
       <c r="B51" t="n">
-        <v>91560</v>
+        <v>91540</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5510,21 +5510,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5534,10 +5534,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>626287</v>
+        <v>626191</v>
       </c>
       <c r="R51" t="n">
-        <v>6987723</v>
+        <v>6987805</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5596,10 +5596,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128900394</v>
+        <v>128900391</v>
       </c>
       <c r="B52" t="n">
-        <v>91950</v>
+        <v>91540</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5607,16 +5607,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5670,7 +5675,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5689,10 +5693,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128900391</v>
+        <v>128900394</v>
       </c>
       <c r="B53" t="n">
-        <v>91542</v>
+        <v>91958</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5700,21 +5704,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5768,6 +5767,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 25307-2025 artfynd.xlsx
+++ b/artfynd/A 25307-2025 artfynd.xlsx
@@ -4238,32 +4238,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128900396</v>
+        <v>128900379</v>
       </c>
       <c r="B38" t="n">
-        <v>91837</v>
+        <v>95931</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>2809</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4273,10 +4273,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>626327</v>
+        <v>626178</v>
       </c>
       <c r="R38" t="n">
-        <v>6987951</v>
+        <v>6987902</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4335,32 +4335,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128900379</v>
+        <v>128900396</v>
       </c>
       <c r="B39" t="n">
-        <v>95930</v>
+        <v>91838</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2809</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4370,10 +4370,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>626178</v>
+        <v>626327</v>
       </c>
       <c r="R39" t="n">
-        <v>6987902</v>
+        <v>6987951</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4432,10 +4432,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128900389</v>
+        <v>128900406</v>
       </c>
       <c r="B40" t="n">
-        <v>91540</v>
+        <v>80146</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4443,21 +4443,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4467,10 +4467,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>626180</v>
+        <v>626294</v>
       </c>
       <c r="R40" t="n">
-        <v>6987905</v>
+        <v>6987721</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4529,10 +4529,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128900406</v>
+        <v>128900389</v>
       </c>
       <c r="B41" t="n">
-        <v>80146</v>
+        <v>91540</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4540,21 +4540,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4564,10 +4564,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>626294</v>
+        <v>626180</v>
       </c>
       <c r="R41" t="n">
-        <v>6987721</v>
+        <v>6987905</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4726,7 +4726,7 @@
         <v>128900384</v>
       </c>
       <c r="B43" t="n">
-        <v>92230</v>
+        <v>92231</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>128900386</v>
       </c>
       <c r="B46" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>128900376</v>
       </c>
       <c r="B47" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5211,7 +5211,7 @@
         <v>128900393</v>
       </c>
       <c r="B48" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5402,10 +5402,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128900408</v>
+        <v>128900410</v>
       </c>
       <c r="B50" t="n">
-        <v>91558</v>
+        <v>91540</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5413,21 +5413,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5437,10 +5437,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>626287</v>
+        <v>626191</v>
       </c>
       <c r="R50" t="n">
-        <v>6987723</v>
+        <v>6987805</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5499,10 +5499,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128900410</v>
+        <v>128900408</v>
       </c>
       <c r="B51" t="n">
-        <v>91540</v>
+        <v>91560</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5510,23 +5510,19 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -5534,10 +5530,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>626191</v>
+        <v>626287</v>
       </c>
       <c r="R51" t="n">
-        <v>6987805</v>
+        <v>6987723</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5696,7 +5692,7 @@
         <v>128900394</v>
       </c>
       <c r="B53" t="n">
-        <v>91958</v>
+        <v>91959</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 25307-2025 artfynd.xlsx
+++ b/artfynd/A 25307-2025 artfynd.xlsx
@@ -4238,32 +4238,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128900379</v>
+        <v>128900396</v>
       </c>
       <c r="B38" t="n">
-        <v>95931</v>
+        <v>91838</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2809</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4273,10 +4273,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>626178</v>
+        <v>626327</v>
       </c>
       <c r="R38" t="n">
-        <v>6987902</v>
+        <v>6987951</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4335,32 +4335,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128900396</v>
+        <v>128900379</v>
       </c>
       <c r="B39" t="n">
-        <v>91838</v>
+        <v>95932</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>2809</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4370,10 +4370,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>626327</v>
+        <v>626178</v>
       </c>
       <c r="R39" t="n">
-        <v>6987951</v>
+        <v>6987902</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>

--- a/artfynd/A 25307-2025 artfynd.xlsx
+++ b/artfynd/A 25307-2025 artfynd.xlsx
@@ -4241,7 +4241,7 @@
         <v>128900396</v>
       </c>
       <c r="B38" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4338,7 +4338,7 @@
         <v>128900379</v>
       </c>
       <c r="B39" t="n">
-        <v>95932</v>
+        <v>95936</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         <v>128900406</v>
       </c>
       <c r="B40" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>128900389</v>
       </c>
       <c r="B41" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4626,32 +4626,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128900398</v>
+        <v>128900384</v>
       </c>
       <c r="B42" t="n">
-        <v>91554</v>
+        <v>92234</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1204</v>
+        <v>898</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4661,10 +4661,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>626317</v>
+        <v>626176</v>
       </c>
       <c r="R42" t="n">
-        <v>6987956</v>
+        <v>6987909</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4723,32 +4723,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128900384</v>
+        <v>128900398</v>
       </c>
       <c r="B43" t="n">
-        <v>92231</v>
+        <v>91557</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>898</v>
+        <v>1204</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4758,10 +4758,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>626176</v>
+        <v>626317</v>
       </c>
       <c r="R43" t="n">
-        <v>6987909</v>
+        <v>6987956</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4823,7 +4823,7 @@
         <v>128900400</v>
       </c>
       <c r="B44" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4920,7 +4920,7 @@
         <v>128900402</v>
       </c>
       <c r="B45" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>128900386</v>
       </c>
       <c r="B46" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>128900376</v>
       </c>
       <c r="B47" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5211,7 +5211,7 @@
         <v>128900393</v>
       </c>
       <c r="B48" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
         <v>128900404</v>
       </c>
       <c r="B49" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5402,10 +5402,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128900410</v>
+        <v>128900408</v>
       </c>
       <c r="B50" t="n">
-        <v>91540</v>
+        <v>91563</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5413,23 +5413,19 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -5437,10 +5433,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>626191</v>
+        <v>626287</v>
       </c>
       <c r="R50" t="n">
-        <v>6987805</v>
+        <v>6987723</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5499,10 +5495,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128900408</v>
+        <v>128900410</v>
       </c>
       <c r="B51" t="n">
-        <v>91560</v>
+        <v>91543</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5510,19 +5506,23 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -5530,10 +5530,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>626287</v>
+        <v>626191</v>
       </c>
       <c r="R51" t="n">
-        <v>6987723</v>
+        <v>6987805</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5595,7 +5595,7 @@
         <v>128900391</v>
       </c>
       <c r="B52" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>128900394</v>
       </c>
       <c r="B53" t="n">
-        <v>91959</v>
+        <v>91962</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 25307-2025 artfynd.xlsx
+++ b/artfynd/A 25307-2025 artfynd.xlsx
@@ -4238,32 +4238,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128900396</v>
+        <v>128900379</v>
       </c>
       <c r="B38" t="n">
-        <v>91841</v>
+        <v>95936</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>2809</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4273,10 +4273,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>626327</v>
+        <v>626178</v>
       </c>
       <c r="R38" t="n">
-        <v>6987951</v>
+        <v>6987902</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4335,32 +4335,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128900379</v>
+        <v>128900396</v>
       </c>
       <c r="B39" t="n">
-        <v>95936</v>
+        <v>91841</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2809</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4370,10 +4370,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>626178</v>
+        <v>626327</v>
       </c>
       <c r="R39" t="n">
-        <v>6987902</v>
+        <v>6987951</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5402,10 +5402,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128900408</v>
+        <v>128900410</v>
       </c>
       <c r="B50" t="n">
-        <v>91563</v>
+        <v>91543</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5413,19 +5413,23 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -5433,10 +5437,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>626287</v>
+        <v>626191</v>
       </c>
       <c r="R50" t="n">
-        <v>6987723</v>
+        <v>6987805</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5495,10 +5499,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128900410</v>
+        <v>128900408</v>
       </c>
       <c r="B51" t="n">
-        <v>91543</v>
+        <v>91563</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5506,23 +5510,19 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -5530,10 +5530,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>626191</v>
+        <v>626287</v>
       </c>
       <c r="R51" t="n">
-        <v>6987805</v>
+        <v>6987723</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>

--- a/artfynd/A 25307-2025 artfynd.xlsx
+++ b/artfynd/A 25307-2025 artfynd.xlsx
@@ -4241,7 +4241,7 @@
         <v>128900379</v>
       </c>
       <c r="B38" t="n">
-        <v>95936</v>
+        <v>95938</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4338,7 +4338,7 @@
         <v>128900396</v>
       </c>
       <c r="B39" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4432,10 +4432,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128900406</v>
+        <v>128900389</v>
       </c>
       <c r="B40" t="n">
-        <v>80148</v>
+        <v>91545</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4443,21 +4443,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4467,10 +4467,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>626294</v>
+        <v>626180</v>
       </c>
       <c r="R40" t="n">
-        <v>6987721</v>
+        <v>6987905</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4529,10 +4529,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128900389</v>
+        <v>128900406</v>
       </c>
       <c r="B41" t="n">
-        <v>91543</v>
+        <v>80149</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4540,21 +4540,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4564,10 +4564,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>626180</v>
+        <v>626294</v>
       </c>
       <c r="R41" t="n">
-        <v>6987905</v>
+        <v>6987721</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4626,32 +4626,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128900384</v>
+        <v>128900398</v>
       </c>
       <c r="B42" t="n">
-        <v>92234</v>
+        <v>91559</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>898</v>
+        <v>1204</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4661,10 +4661,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>626176</v>
+        <v>626317</v>
       </c>
       <c r="R42" t="n">
-        <v>6987909</v>
+        <v>6987956</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4723,10 +4723,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128900398</v>
+        <v>128900400</v>
       </c>
       <c r="B43" t="n">
-        <v>91557</v>
+        <v>91545</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4734,21 +4734,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4758,10 +4758,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>626317</v>
+        <v>626273</v>
       </c>
       <c r="R43" t="n">
-        <v>6987956</v>
+        <v>6987791</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4820,32 +4820,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128900400</v>
+        <v>128900384</v>
       </c>
       <c r="B44" t="n">
-        <v>91543</v>
+        <v>92236</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>898</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4855,10 +4855,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>626273</v>
+        <v>626176</v>
       </c>
       <c r="R44" t="n">
-        <v>6987791</v>
+        <v>6987909</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4920,7 +4920,7 @@
         <v>128900402</v>
       </c>
       <c r="B45" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>128900386</v>
       </c>
       <c r="B46" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>128900376</v>
       </c>
       <c r="B47" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5211,7 +5211,7 @@
         <v>128900393</v>
       </c>
       <c r="B48" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
         <v>128900404</v>
       </c>
       <c r="B49" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5402,10 +5402,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128900410</v>
+        <v>128900408</v>
       </c>
       <c r="B50" t="n">
-        <v>91543</v>
+        <v>91565</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5413,23 +5413,19 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -5437,10 +5433,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>626191</v>
+        <v>626287</v>
       </c>
       <c r="R50" t="n">
-        <v>6987805</v>
+        <v>6987723</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5499,10 +5495,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128900408</v>
+        <v>128900410</v>
       </c>
       <c r="B51" t="n">
-        <v>91563</v>
+        <v>91545</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5510,19 +5506,23 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -5530,10 +5530,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>626287</v>
+        <v>626191</v>
       </c>
       <c r="R51" t="n">
-        <v>6987723</v>
+        <v>6987805</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5592,10 +5592,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128900391</v>
+        <v>128900394</v>
       </c>
       <c r="B52" t="n">
-        <v>91543</v>
+        <v>91964</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5603,21 +5603,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5671,6 +5666,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5689,10 +5685,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128900394</v>
+        <v>128900391</v>
       </c>
       <c r="B53" t="n">
-        <v>91962</v>
+        <v>91545</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5700,16 +5696,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5763,7 +5764,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 25307-2025 artfynd.xlsx
+++ b/artfynd/A 25307-2025 artfynd.xlsx
@@ -819,7 +819,7 @@
         <v>126964623</v>
       </c>
       <c r="B3" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 25307-2025 artfynd.xlsx
+++ b/artfynd/A 25307-2025 artfynd.xlsx
@@ -819,7 +819,7 @@
         <v>126964623</v>
       </c>
       <c r="B3" t="n">
-        <v>79011</v>
+        <v>79020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
